--- a/data.mn/public/datasets/weekly-meat-prices-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/weekly-meat-prices-ulaanbaatar.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6771,6 +6771,182 @@
         <v>25930</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>31457</v>
+      </c>
+      <c r="C289" t="n">
+        <v>35724</v>
+      </c>
+      <c r="D289" t="n">
+        <v>20984</v>
+      </c>
+      <c r="E289" t="n">
+        <v>18464</v>
+      </c>
+      <c r="F289" t="n">
+        <v>26342</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>31186</v>
+      </c>
+      <c r="C290" t="n">
+        <v>34821</v>
+      </c>
+      <c r="D290" t="n">
+        <v>20984</v>
+      </c>
+      <c r="E290" t="n">
+        <v>18539</v>
+      </c>
+      <c r="F290" t="n">
+        <v>26294</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>31091</v>
+      </c>
+      <c r="C291" t="n">
+        <v>34821</v>
+      </c>
+      <c r="D291" t="n">
+        <v>20824</v>
+      </c>
+      <c r="E291" t="n">
+        <v>18449</v>
+      </c>
+      <c r="F291" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>31106</v>
+      </c>
+      <c r="C292" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D292" t="n">
+        <v>20824</v>
+      </c>
+      <c r="E292" t="n">
+        <v>18116</v>
+      </c>
+      <c r="F292" t="n">
+        <v>25923</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>30804</v>
+      </c>
+      <c r="C293" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D293" t="n">
+        <v>20661</v>
+      </c>
+      <c r="E293" t="n">
+        <v>18389</v>
+      </c>
+      <c r="F293" t="n">
+        <v>25674</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>30695</v>
+      </c>
+      <c r="C294" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D294" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E294" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F294" t="n">
+        <v>25519</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>30270</v>
+      </c>
+      <c r="C295" t="n">
+        <v>34376</v>
+      </c>
+      <c r="D295" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E295" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F295" t="n">
+        <v>25480</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>29709</v>
+      </c>
+      <c r="C296" t="n">
+        <v>33663</v>
+      </c>
+      <c r="D296" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E296" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F296" t="n">
+        <v>25434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6782,14 +6958,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -6801,27 +6977,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Үхрийн мах, ястай, кг</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Үхрийн мах, цул, кг</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ямааны мах, ястай, кг</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Адууны мах, ястай, кг</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Хонины мах, ястай, кг</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Ямааны мах, ястай, кг</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Үхрийн мах, цул, кг</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Үхрийн мах, ястай, кг</t>
         </is>
       </c>
     </row>
@@ -6832,19 +7008,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9091</v>
+        <v>11371</v>
       </c>
       <c r="C2" t="n">
-        <v>8728</v>
+        <v>12564</v>
       </c>
       <c r="D2" t="n">
         <v>7500</v>
       </c>
       <c r="E2" t="n">
-        <v>12564</v>
+        <v>9091</v>
       </c>
       <c r="F2" t="n">
-        <v>11371</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="3">
@@ -6854,19 +7030,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9028</v>
+        <v>11396</v>
       </c>
       <c r="C3" t="n">
-        <v>8797</v>
+        <v>12795</v>
       </c>
       <c r="D3" t="n">
         <v>7800</v>
       </c>
       <c r="E3" t="n">
-        <v>12795</v>
+        <v>9028</v>
       </c>
       <c r="F3" t="n">
-        <v>11396</v>
+        <v>8797</v>
       </c>
     </row>
     <row r="4">
@@ -6876,19 +7052,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9028</v>
+        <v>11746</v>
       </c>
       <c r="C4" t="n">
-        <v>9261</v>
+        <v>13014</v>
       </c>
       <c r="D4" t="n">
         <v>7800</v>
       </c>
       <c r="E4" t="n">
-        <v>13014</v>
+        <v>9028</v>
       </c>
       <c r="F4" t="n">
-        <v>11746</v>
+        <v>9261</v>
       </c>
     </row>
     <row r="5">
@@ -6898,19 +7074,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9028</v>
+        <v>11952</v>
       </c>
       <c r="C5" t="n">
-        <v>9368</v>
+        <v>13305</v>
       </c>
       <c r="D5" t="n">
         <v>7899</v>
       </c>
       <c r="E5" t="n">
-        <v>13305</v>
+        <v>9028</v>
       </c>
       <c r="F5" t="n">
-        <v>11952</v>
+        <v>9368</v>
       </c>
     </row>
     <row r="6">
@@ -6920,19 +7096,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9643</v>
+        <v>12863</v>
       </c>
       <c r="C6" t="n">
-        <v>10554</v>
+        <v>14708</v>
       </c>
       <c r="D6" t="n">
         <v>8746</v>
       </c>
       <c r="E6" t="n">
-        <v>14708</v>
+        <v>9643</v>
       </c>
       <c r="F6" t="n">
-        <v>12863</v>
+        <v>10554</v>
       </c>
     </row>
     <row r="7">
@@ -6942,19 +7118,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9577</v>
+        <v>12604</v>
       </c>
       <c r="C7" t="n">
-        <v>10579</v>
+        <v>14428</v>
       </c>
       <c r="D7" t="n">
         <v>8746</v>
       </c>
       <c r="E7" t="n">
-        <v>14428</v>
+        <v>9577</v>
       </c>
       <c r="F7" t="n">
-        <v>12604</v>
+        <v>10579</v>
       </c>
     </row>
     <row r="8">
@@ -6964,19 +7140,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9577</v>
+        <v>12492</v>
       </c>
       <c r="C8" t="n">
-        <v>10458</v>
+        <v>14378</v>
       </c>
       <c r="D8" t="n">
         <v>8746</v>
       </c>
       <c r="E8" t="n">
-        <v>14378</v>
+        <v>9577</v>
       </c>
       <c r="F8" t="n">
-        <v>12492</v>
+        <v>10458</v>
       </c>
     </row>
     <row r="9">
@@ -6986,19 +7162,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9643</v>
+        <v>12466</v>
       </c>
       <c r="C9" t="n">
-        <v>10248</v>
+        <v>14230</v>
       </c>
       <c r="D9" t="n">
         <v>8746</v>
       </c>
       <c r="E9" t="n">
-        <v>14230</v>
+        <v>9643</v>
       </c>
       <c r="F9" t="n">
-        <v>12466</v>
+        <v>10248</v>
       </c>
     </row>
     <row r="10">
@@ -7008,19 +7184,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9643</v>
+        <v>12416</v>
       </c>
       <c r="C10" t="n">
-        <v>10229</v>
+        <v>14230</v>
       </c>
       <c r="D10" t="n">
         <v>8746</v>
       </c>
       <c r="E10" t="n">
-        <v>14230</v>
+        <v>9643</v>
       </c>
       <c r="F10" t="n">
-        <v>12416</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="11">
@@ -7030,19 +7206,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9747</v>
+        <v>12423</v>
       </c>
       <c r="C11" t="n">
-        <v>10279</v>
+        <v>14226</v>
       </c>
       <c r="D11" t="n">
         <v>8746</v>
       </c>
       <c r="E11" t="n">
-        <v>14226</v>
+        <v>9747</v>
       </c>
       <c r="F11" t="n">
-        <v>12423</v>
+        <v>10279</v>
       </c>
     </row>
     <row r="12">
@@ -7052,19 +7228,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9984</v>
+        <v>12325</v>
       </c>
       <c r="C12" t="n">
-        <v>10400</v>
+        <v>14323</v>
       </c>
       <c r="D12" t="n">
         <v>8746</v>
       </c>
       <c r="E12" t="n">
-        <v>14323</v>
+        <v>9984</v>
       </c>
       <c r="F12" t="n">
-        <v>12325</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="13">
@@ -7074,19 +7250,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11100</v>
+        <v>12983</v>
       </c>
       <c r="C13" t="n">
-        <v>11197</v>
+        <v>14945</v>
       </c>
       <c r="D13" t="n">
         <v>9143</v>
       </c>
       <c r="E13" t="n">
-        <v>14945</v>
+        <v>11100</v>
       </c>
       <c r="F13" t="n">
-        <v>12983</v>
+        <v>11197</v>
       </c>
     </row>
     <row r="14">
@@ -7096,19 +7272,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11929</v>
+        <v>13208</v>
       </c>
       <c r="C14" t="n">
-        <v>11414</v>
+        <v>15196</v>
       </c>
       <c r="D14" t="n">
         <v>9143</v>
       </c>
       <c r="E14" t="n">
-        <v>15196</v>
+        <v>11929</v>
       </c>
       <c r="F14" t="n">
-        <v>13208</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="15">
@@ -7118,19 +7294,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12353</v>
+        <v>13636</v>
       </c>
       <c r="C15" t="n">
-        <v>11941</v>
+        <v>15664</v>
       </c>
       <c r="D15" t="n">
         <v>9143</v>
       </c>
       <c r="E15" t="n">
-        <v>15664</v>
+        <v>12353</v>
       </c>
       <c r="F15" t="n">
-        <v>13636</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="16">
@@ -7140,19 +7316,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12708</v>
+        <v>13862</v>
       </c>
       <c r="C16" t="n">
-        <v>12468</v>
+        <v>16058</v>
       </c>
       <c r="D16" t="n">
         <v>9987</v>
       </c>
       <c r="E16" t="n">
-        <v>16058</v>
+        <v>12708</v>
       </c>
       <c r="F16" t="n">
-        <v>13862</v>
+        <v>12468</v>
       </c>
     </row>
     <row r="17">
@@ -7162,19 +7338,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12844</v>
+        <v>13910</v>
       </c>
       <c r="C17" t="n">
-        <v>12410</v>
+        <v>15926</v>
       </c>
       <c r="D17" t="n">
         <v>9987</v>
       </c>
       <c r="E17" t="n">
-        <v>15926</v>
+        <v>12844</v>
       </c>
       <c r="F17" t="n">
-        <v>13910</v>
+        <v>12410</v>
       </c>
     </row>
     <row r="18">
@@ -7184,19 +7360,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12976</v>
+        <v>14005</v>
       </c>
       <c r="C18" t="n">
-        <v>12460</v>
+        <v>16030</v>
       </c>
       <c r="D18" t="n">
         <v>9987</v>
       </c>
       <c r="E18" t="n">
-        <v>16030</v>
+        <v>12976</v>
       </c>
       <c r="F18" t="n">
-        <v>14005</v>
+        <v>12460</v>
       </c>
     </row>
     <row r="19">
@@ -7206,19 +7382,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13104</v>
+        <v>13957</v>
       </c>
       <c r="C19" t="n">
-        <v>12460</v>
+        <v>15964</v>
       </c>
       <c r="D19" t="n">
         <v>9987</v>
       </c>
       <c r="E19" t="n">
-        <v>15964</v>
+        <v>13104</v>
       </c>
       <c r="F19" t="n">
-        <v>13957</v>
+        <v>12460</v>
       </c>
     </row>
     <row r="20">
@@ -7228,19 +7404,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12935</v>
+        <v>13931</v>
       </c>
       <c r="C20" t="n">
-        <v>12434</v>
+        <v>16001</v>
       </c>
       <c r="D20" t="n">
         <v>9987</v>
       </c>
       <c r="E20" t="n">
-        <v>16001</v>
+        <v>12935</v>
       </c>
       <c r="F20" t="n">
-        <v>13931</v>
+        <v>12434</v>
       </c>
     </row>
     <row r="21">
@@ -7250,19 +7426,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13694</v>
+        <v>13944</v>
       </c>
       <c r="C21" t="n">
-        <v>12435</v>
+        <v>16038</v>
       </c>
       <c r="D21" t="n">
         <v>10144</v>
       </c>
       <c r="E21" t="n">
-        <v>16038</v>
+        <v>13694</v>
       </c>
       <c r="F21" t="n">
-        <v>13944</v>
+        <v>12435</v>
       </c>
     </row>
     <row r="22">
@@ -7272,19 +7448,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13560</v>
+        <v>13990</v>
       </c>
       <c r="C22" t="n">
-        <v>12231</v>
+        <v>15984</v>
       </c>
       <c r="D22" t="n">
         <v>10144</v>
       </c>
       <c r="E22" t="n">
-        <v>15984</v>
+        <v>13560</v>
       </c>
       <c r="F22" t="n">
-        <v>13990</v>
+        <v>12231</v>
       </c>
     </row>
     <row r="23">
@@ -7294,19 +7470,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13694</v>
+        <v>14563</v>
       </c>
       <c r="C23" t="n">
-        <v>12630</v>
+        <v>16622</v>
       </c>
       <c r="D23" t="n">
         <v>10144</v>
       </c>
       <c r="E23" t="n">
-        <v>16622</v>
+        <v>13694</v>
       </c>
       <c r="F23" t="n">
-        <v>14563</v>
+        <v>12630</v>
       </c>
     </row>
     <row r="24">
@@ -7316,19 +7492,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13349</v>
+        <v>14603</v>
       </c>
       <c r="C24" t="n">
-        <v>12664</v>
+        <v>16565</v>
       </c>
       <c r="D24" t="n">
         <v>10383</v>
       </c>
       <c r="E24" t="n">
-        <v>16565</v>
+        <v>13349</v>
       </c>
       <c r="F24" t="n">
-        <v>14603</v>
+        <v>12664</v>
       </c>
     </row>
     <row r="25">
@@ -7338,19 +7514,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13349</v>
+        <v>14576</v>
       </c>
       <c r="C25" t="n">
-        <v>12611</v>
+        <v>16538</v>
       </c>
       <c r="D25" t="n">
         <v>10383</v>
       </c>
       <c r="E25" t="n">
-        <v>16538</v>
+        <v>13349</v>
       </c>
       <c r="F25" t="n">
-        <v>14576</v>
+        <v>12611</v>
       </c>
     </row>
     <row r="26">
@@ -7360,19 +7536,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12844</v>
+        <v>15141</v>
       </c>
       <c r="C26" t="n">
-        <v>12907</v>
+        <v>16787</v>
       </c>
       <c r="D26" t="n">
         <v>10488</v>
       </c>
       <c r="E26" t="n">
-        <v>16787</v>
+        <v>12844</v>
       </c>
       <c r="F26" t="n">
-        <v>15141</v>
+        <v>12907</v>
       </c>
     </row>
     <row r="27">
@@ -7382,19 +7558,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13208</v>
+        <v>14967</v>
       </c>
       <c r="C27" t="n">
-        <v>12669</v>
+        <v>16601</v>
       </c>
       <c r="D27" t="n">
         <v>10488</v>
       </c>
       <c r="E27" t="n">
-        <v>16601</v>
+        <v>13208</v>
       </c>
       <c r="F27" t="n">
-        <v>14967</v>
+        <v>12669</v>
       </c>
     </row>
     <row r="28">
@@ -7404,19 +7580,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12981</v>
+        <v>15129</v>
       </c>
       <c r="C28" t="n">
-        <v>12620</v>
+        <v>16746</v>
       </c>
       <c r="D28" t="n">
         <v>10488</v>
       </c>
       <c r="E28" t="n">
-        <v>16746</v>
+        <v>12981</v>
       </c>
       <c r="F28" t="n">
-        <v>15129</v>
+        <v>12620</v>
       </c>
     </row>
     <row r="29">
@@ -7426,19 +7602,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12981</v>
+        <v>15129</v>
       </c>
       <c r="C29" t="n">
-        <v>12620</v>
+        <v>16809</v>
       </c>
       <c r="D29" t="n">
         <v>10488</v>
       </c>
       <c r="E29" t="n">
-        <v>16809</v>
+        <v>12981</v>
       </c>
       <c r="F29" t="n">
-        <v>15129</v>
+        <v>12620</v>
       </c>
     </row>
     <row r="30">
@@ -7448,19 +7624,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11344</v>
+        <v>14660</v>
       </c>
       <c r="C30" t="n">
-        <v>12303</v>
+        <v>16492</v>
       </c>
       <c r="D30" t="n">
         <v>10488</v>
       </c>
       <c r="E30" t="n">
-        <v>16492</v>
+        <v>11344</v>
       </c>
       <c r="F30" t="n">
-        <v>14660</v>
+        <v>12303</v>
       </c>
     </row>
     <row r="31">
@@ -7470,19 +7646,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10692</v>
+        <v>14272</v>
       </c>
       <c r="C31" t="n">
-        <v>12222</v>
+        <v>16139</v>
       </c>
       <c r="D31" t="n">
         <v>10488</v>
       </c>
       <c r="E31" t="n">
-        <v>16139</v>
+        <v>10692</v>
       </c>
       <c r="F31" t="n">
-        <v>14272</v>
+        <v>12222</v>
       </c>
     </row>
     <row r="32">
@@ -7492,19 +7668,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10741</v>
+        <v>13900</v>
       </c>
       <c r="C32" t="n">
-        <v>11615</v>
+        <v>15513</v>
       </c>
       <c r="D32" t="n">
         <v>10488</v>
       </c>
       <c r="E32" t="n">
-        <v>15513</v>
+        <v>10741</v>
       </c>
       <c r="F32" t="n">
-        <v>13900</v>
+        <v>11615</v>
       </c>
     </row>
     <row r="33">
@@ -7514,19 +7690,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10741</v>
+        <v>13855</v>
       </c>
       <c r="C33" t="n">
-        <v>11598</v>
+        <v>15506</v>
       </c>
       <c r="D33" t="n">
         <v>10488</v>
       </c>
       <c r="E33" t="n">
-        <v>15506</v>
+        <v>10741</v>
       </c>
       <c r="F33" t="n">
-        <v>13855</v>
+        <v>11598</v>
       </c>
     </row>
     <row r="34">
@@ -7536,19 +7712,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9833</v>
+        <v>13537</v>
       </c>
       <c r="C34" t="n">
-        <v>11162</v>
+        <v>15331</v>
       </c>
       <c r="D34" t="n">
         <v>9000</v>
       </c>
       <c r="E34" t="n">
-        <v>15331</v>
+        <v>9833</v>
       </c>
       <c r="F34" t="n">
-        <v>13537</v>
+        <v>11162</v>
       </c>
     </row>
     <row r="35">
@@ -7558,19 +7734,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10241</v>
+        <v>13514</v>
       </c>
       <c r="C35" t="n">
-        <v>11152</v>
+        <v>15328</v>
       </c>
       <c r="D35" t="n">
         <v>9000</v>
       </c>
       <c r="E35" t="n">
-        <v>15328</v>
+        <v>10241</v>
       </c>
       <c r="F35" t="n">
-        <v>13514</v>
+        <v>11152</v>
       </c>
     </row>
     <row r="36">
@@ -7580,19 +7756,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9975</v>
+        <v>13575</v>
       </c>
       <c r="C36" t="n">
-        <v>11145</v>
+        <v>15388</v>
       </c>
       <c r="D36" t="n">
         <v>8643</v>
       </c>
       <c r="E36" t="n">
-        <v>15388</v>
+        <v>9975</v>
       </c>
       <c r="F36" t="n">
-        <v>13575</v>
+        <v>11145</v>
       </c>
     </row>
     <row r="37">
@@ -7602,19 +7778,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10111</v>
+        <v>13516</v>
       </c>
       <c r="C37" t="n">
-        <v>11090</v>
+        <v>15279</v>
       </c>
       <c r="D37" t="n">
         <v>8643</v>
       </c>
       <c r="E37" t="n">
-        <v>15279</v>
+        <v>10111</v>
       </c>
       <c r="F37" t="n">
-        <v>13516</v>
+        <v>11090</v>
       </c>
     </row>
     <row r="38">
@@ -7624,19 +7800,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10111</v>
+        <v>13216</v>
       </c>
       <c r="C38" t="n">
-        <v>10906</v>
+        <v>14889</v>
       </c>
       <c r="D38" t="n">
         <v>8643</v>
       </c>
       <c r="E38" t="n">
-        <v>14889</v>
+        <v>10111</v>
       </c>
       <c r="F38" t="n">
-        <v>13216</v>
+        <v>10906</v>
       </c>
     </row>
     <row r="39">
@@ -7646,19 +7822,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9833</v>
+        <v>13429</v>
       </c>
       <c r="C39" t="n">
-        <v>10865</v>
+        <v>14912</v>
       </c>
       <c r="D39" t="n">
         <v>8643</v>
       </c>
       <c r="E39" t="n">
-        <v>14912</v>
+        <v>9833</v>
       </c>
       <c r="F39" t="n">
-        <v>13429</v>
+        <v>10865</v>
       </c>
     </row>
     <row r="40">
@@ -7668,19 +7844,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9975</v>
+        <v>13367</v>
       </c>
       <c r="C40" t="n">
-        <v>10865</v>
+        <v>15006</v>
       </c>
       <c r="D40" t="n">
         <v>8643</v>
       </c>
       <c r="E40" t="n">
-        <v>15006</v>
+        <v>9975</v>
       </c>
       <c r="F40" t="n">
-        <v>13367</v>
+        <v>10865</v>
       </c>
     </row>
     <row r="41">
@@ -7690,19 +7866,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10224</v>
+        <v>13304</v>
       </c>
       <c r="C41" t="n">
-        <v>10834</v>
+        <v>15070</v>
       </c>
       <c r="D41" t="n">
         <v>9000</v>
       </c>
       <c r="E41" t="n">
-        <v>15070</v>
+        <v>10224</v>
       </c>
       <c r="F41" t="n">
-        <v>13304</v>
+        <v>10834</v>
       </c>
     </row>
     <row r="42">
@@ -7712,19 +7888,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10224</v>
+        <v>13405</v>
       </c>
       <c r="C42" t="n">
-        <v>11226</v>
+        <v>15272</v>
       </c>
       <c r="D42" t="n">
         <v>9000</v>
       </c>
       <c r="E42" t="n">
-        <v>15272</v>
+        <v>10224</v>
       </c>
       <c r="F42" t="n">
-        <v>13405</v>
+        <v>11226</v>
       </c>
     </row>
     <row r="43">
@@ -7734,19 +7910,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10224</v>
+        <v>13081</v>
       </c>
       <c r="C43" t="n">
-        <v>10996</v>
+        <v>14897</v>
       </c>
       <c r="D43" t="n">
         <v>9000</v>
       </c>
       <c r="E43" t="n">
-        <v>14897</v>
+        <v>10224</v>
       </c>
       <c r="F43" t="n">
-        <v>13081</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="44">
@@ -7756,19 +7932,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9937</v>
+        <v>13322</v>
       </c>
       <c r="C44" t="n">
-        <v>10974</v>
+        <v>15121</v>
       </c>
       <c r="D44" t="n">
         <v>8986</v>
       </c>
       <c r="E44" t="n">
-        <v>15121</v>
+        <v>9937</v>
       </c>
       <c r="F44" t="n">
-        <v>13322</v>
+        <v>10974</v>
       </c>
     </row>
     <row r="45">
@@ -7778,19 +7954,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9937</v>
+        <v>13322</v>
       </c>
       <c r="C45" t="n">
-        <v>10871</v>
+        <v>15078</v>
       </c>
       <c r="D45" t="n">
         <v>8986</v>
       </c>
       <c r="E45" t="n">
-        <v>15078</v>
+        <v>9937</v>
       </c>
       <c r="F45" t="n">
-        <v>13322</v>
+        <v>10871</v>
       </c>
     </row>
     <row r="46">
@@ -7800,19 +7976,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10080</v>
+        <v>13443</v>
       </c>
       <c r="C46" t="n">
-        <v>10849</v>
+        <v>15030</v>
       </c>
       <c r="D46" t="n">
         <v>8986</v>
       </c>
       <c r="E46" t="n">
-        <v>15030</v>
+        <v>10080</v>
       </c>
       <c r="F46" t="n">
-        <v>13443</v>
+        <v>10849</v>
       </c>
     </row>
     <row r="47">
@@ -7822,19 +7998,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9665</v>
+        <v>13556</v>
       </c>
       <c r="C47" t="n">
-        <v>10870</v>
+        <v>15066</v>
       </c>
       <c r="D47" t="n">
         <v>8037</v>
       </c>
       <c r="E47" t="n">
-        <v>15066</v>
+        <v>9665</v>
       </c>
       <c r="F47" t="n">
-        <v>13556</v>
+        <v>10870</v>
       </c>
     </row>
     <row r="48">
@@ -7844,19 +8020,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10217</v>
+        <v>13050</v>
       </c>
       <c r="C48" t="n">
-        <v>10506</v>
+        <v>14785</v>
       </c>
       <c r="D48" t="n">
         <v>8246</v>
       </c>
       <c r="E48" t="n">
-        <v>14785</v>
+        <v>10217</v>
       </c>
       <c r="F48" t="n">
-        <v>13050</v>
+        <v>10506</v>
       </c>
     </row>
     <row r="49">
@@ -7866,19 +8042,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9969</v>
+        <v>13097</v>
       </c>
       <c r="C49" t="n">
-        <v>10415</v>
+        <v>15072</v>
       </c>
       <c r="D49" t="n">
         <v>8500</v>
       </c>
       <c r="E49" t="n">
-        <v>15072</v>
+        <v>9969</v>
       </c>
       <c r="F49" t="n">
-        <v>13097</v>
+        <v>10415</v>
       </c>
     </row>
     <row r="50">
@@ -7888,19 +8064,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9220</v>
+        <v>13305</v>
       </c>
       <c r="C50" t="n">
-        <v>10395</v>
+        <v>15166</v>
       </c>
       <c r="D50" t="n">
         <v>8500</v>
       </c>
       <c r="E50" t="n">
-        <v>15166</v>
+        <v>9220</v>
       </c>
       <c r="F50" t="n">
-        <v>13305</v>
+        <v>10395</v>
       </c>
     </row>
     <row r="51">
@@ -7910,19 +8086,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10109</v>
+        <v>13462</v>
       </c>
       <c r="C51" t="n">
-        <v>10934</v>
+        <v>15269</v>
       </c>
       <c r="D51" t="n">
         <v>8618</v>
       </c>
       <c r="E51" t="n">
-        <v>15269</v>
+        <v>10109</v>
       </c>
       <c r="F51" t="n">
-        <v>13462</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="52">
@@ -7932,19 +8108,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10471</v>
+        <v>13669</v>
       </c>
       <c r="C52" t="n">
-        <v>11266</v>
+        <v>15776</v>
       </c>
       <c r="D52" t="n">
         <v>8608</v>
       </c>
       <c r="E52" t="n">
-        <v>15776</v>
+        <v>10471</v>
       </c>
       <c r="F52" t="n">
-        <v>13669</v>
+        <v>11266</v>
       </c>
     </row>
     <row r="53">
@@ -7954,19 +8130,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10219</v>
+        <v>13945</v>
       </c>
       <c r="C53" t="n">
-        <v>11257</v>
+        <v>15882</v>
       </c>
       <c r="D53" t="n">
         <v>8500</v>
       </c>
       <c r="E53" t="n">
-        <v>15882</v>
+        <v>10219</v>
       </c>
       <c r="F53" t="n">
-        <v>13945</v>
+        <v>11257</v>
       </c>
     </row>
     <row r="54">
@@ -7976,19 +8152,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10034</v>
+        <v>14084</v>
       </c>
       <c r="C54" t="n">
-        <v>11600</v>
+        <v>15837</v>
       </c>
       <c r="D54" t="n">
         <v>8349</v>
       </c>
       <c r="E54" t="n">
-        <v>15837</v>
+        <v>10034</v>
       </c>
       <c r="F54" t="n">
-        <v>14084</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="55">
@@ -7998,19 +8174,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9870</v>
+        <v>14147</v>
       </c>
       <c r="C55" t="n">
-        <v>11706</v>
+        <v>15842</v>
       </c>
       <c r="D55" t="n">
         <v>8649</v>
       </c>
       <c r="E55" t="n">
-        <v>15842</v>
+        <v>9870</v>
       </c>
       <c r="F55" t="n">
-        <v>14147</v>
+        <v>11706</v>
       </c>
     </row>
     <row r="56">
@@ -8020,19 +8196,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9972</v>
+        <v>13943</v>
       </c>
       <c r="C56" t="n">
-        <v>11262</v>
+        <v>15998</v>
       </c>
       <c r="D56" t="n">
         <v>8649</v>
       </c>
       <c r="E56" t="n">
-        <v>15998</v>
+        <v>9972</v>
       </c>
       <c r="F56" t="n">
-        <v>13943</v>
+        <v>11262</v>
       </c>
     </row>
     <row r="57">
@@ -8042,19 +8218,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9972</v>
+        <v>14062</v>
       </c>
       <c r="C57" t="n">
-        <v>11558</v>
+        <v>15757</v>
       </c>
       <c r="D57" t="n">
         <v>8649</v>
       </c>
       <c r="E57" t="n">
-        <v>15757</v>
+        <v>9972</v>
       </c>
       <c r="F57" t="n">
-        <v>14062</v>
+        <v>11558</v>
       </c>
     </row>
     <row r="58">
@@ -8064,19 +8240,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9972</v>
+        <v>13801</v>
       </c>
       <c r="C58" t="n">
-        <v>11728</v>
+        <v>15853</v>
       </c>
       <c r="D58" t="n">
         <v>8649</v>
       </c>
       <c r="E58" t="n">
-        <v>15853</v>
+        <v>9972</v>
       </c>
       <c r="F58" t="n">
-        <v>13801</v>
+        <v>11728</v>
       </c>
     </row>
     <row r="59">
@@ -8086,19 +8262,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10161</v>
+        <v>13963</v>
       </c>
       <c r="C59" t="n">
-        <v>11803</v>
+        <v>16104</v>
       </c>
       <c r="D59" t="n">
         <v>8599</v>
       </c>
       <c r="E59" t="n">
-        <v>16104</v>
+        <v>10161</v>
       </c>
       <c r="F59" t="n">
-        <v>13963</v>
+        <v>11803</v>
       </c>
     </row>
     <row r="60">
@@ -8108,19 +8284,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10741</v>
+        <v>14235</v>
       </c>
       <c r="C60" t="n">
-        <v>12293</v>
+        <v>16347</v>
       </c>
       <c r="D60" t="n">
         <v>8599</v>
       </c>
       <c r="E60" t="n">
-        <v>16347</v>
+        <v>10741</v>
       </c>
       <c r="F60" t="n">
-        <v>14235</v>
+        <v>12293</v>
       </c>
     </row>
     <row r="61">
@@ -8130,19 +8306,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10741</v>
+        <v>14202</v>
       </c>
       <c r="C61" t="n">
-        <v>12558</v>
+        <v>16195</v>
       </c>
       <c r="D61" t="n">
         <v>9747</v>
       </c>
       <c r="E61" t="n">
-        <v>16195</v>
+        <v>10741</v>
       </c>
       <c r="F61" t="n">
-        <v>14202</v>
+        <v>12558</v>
       </c>
     </row>
     <row r="62">
@@ -8152,19 +8328,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10741</v>
+        <v>14543</v>
       </c>
       <c r="C62" t="n">
-        <v>12670</v>
+        <v>16300</v>
       </c>
       <c r="D62" t="n">
         <v>9247</v>
       </c>
       <c r="E62" t="n">
-        <v>16300</v>
+        <v>10741</v>
       </c>
       <c r="F62" t="n">
-        <v>14543</v>
+        <v>12670</v>
       </c>
     </row>
     <row r="63">
@@ -8174,19 +8350,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10277</v>
+        <v>13847</v>
       </c>
       <c r="C63" t="n">
-        <v>12310</v>
+        <v>16263</v>
       </c>
       <c r="D63" t="n">
         <v>9391</v>
       </c>
       <c r="E63" t="n">
-        <v>16263</v>
+        <v>10277</v>
       </c>
       <c r="F63" t="n">
-        <v>13847</v>
+        <v>12310</v>
       </c>
     </row>
     <row r="64">
@@ -8196,19 +8372,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10442</v>
+        <v>14571</v>
       </c>
       <c r="C64" t="n">
-        <v>12782</v>
+        <v>16486</v>
       </c>
       <c r="D64" t="n">
         <v>9850</v>
       </c>
       <c r="E64" t="n">
-        <v>16486</v>
+        <v>10442</v>
       </c>
       <c r="F64" t="n">
-        <v>14571</v>
+        <v>12782</v>
       </c>
     </row>
     <row r="65">
@@ -8218,19 +8394,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>10442</v>
+        <v>14126</v>
       </c>
       <c r="C65" t="n">
-        <v>12610</v>
+        <v>16530</v>
       </c>
       <c r="D65" t="n">
         <v>9850</v>
       </c>
       <c r="E65" t="n">
-        <v>16530</v>
+        <v>10442</v>
       </c>
       <c r="F65" t="n">
-        <v>14126</v>
+        <v>12610</v>
       </c>
     </row>
     <row r="66">
@@ -8240,19 +8416,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>10856</v>
+        <v>14234</v>
       </c>
       <c r="C66" t="n">
-        <v>12911</v>
+        <v>16199</v>
       </c>
       <c r="D66" t="n">
         <v>9850</v>
       </c>
       <c r="E66" t="n">
-        <v>16199</v>
+        <v>10856</v>
       </c>
       <c r="F66" t="n">
-        <v>14234</v>
+        <v>12911</v>
       </c>
     </row>
     <row r="67">
@@ -8262,19 +8438,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>10393</v>
+        <v>14569</v>
       </c>
       <c r="C67" t="n">
-        <v>12603</v>
+        <v>16756</v>
       </c>
       <c r="D67" t="n">
         <v>9850</v>
       </c>
       <c r="E67" t="n">
-        <v>16756</v>
+        <v>10393</v>
       </c>
       <c r="F67" t="n">
-        <v>14569</v>
+        <v>12603</v>
       </c>
     </row>
     <row r="68">
@@ -8284,19 +8460,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10571</v>
+        <v>14820</v>
       </c>
       <c r="C68" t="n">
-        <v>12433</v>
+        <v>17041</v>
       </c>
       <c r="D68" t="n">
         <v>9850</v>
       </c>
       <c r="E68" t="n">
-        <v>17041</v>
+        <v>10571</v>
       </c>
       <c r="F68" t="n">
-        <v>14820</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="69">
@@ -8306,19 +8482,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11152</v>
+        <v>14511</v>
       </c>
       <c r="C69" t="n">
-        <v>12538</v>
+        <v>17059</v>
       </c>
       <c r="D69" t="n">
         <v>9850</v>
       </c>
       <c r="E69" t="n">
-        <v>17059</v>
+        <v>11152</v>
       </c>
       <c r="F69" t="n">
-        <v>14511</v>
+        <v>12538</v>
       </c>
     </row>
     <row r="70">
@@ -8328,19 +8504,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10823</v>
+        <v>15068</v>
       </c>
       <c r="C70" t="n">
-        <v>12485</v>
+        <v>17212</v>
       </c>
       <c r="D70" t="n">
         <v>9850</v>
       </c>
       <c r="E70" t="n">
-        <v>17212</v>
+        <v>10823</v>
       </c>
       <c r="F70" t="n">
-        <v>15068</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="71">
@@ -8350,19 +8526,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11381</v>
+        <v>15205</v>
       </c>
       <c r="C71" t="n">
-        <v>12682</v>
+        <v>17214</v>
       </c>
       <c r="D71" t="n">
         <v>9698</v>
       </c>
       <c r="E71" t="n">
-        <v>17214</v>
+        <v>11381</v>
       </c>
       <c r="F71" t="n">
-        <v>15205</v>
+        <v>12682</v>
       </c>
     </row>
     <row r="72">
@@ -8372,19 +8548,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11238</v>
+        <v>15207</v>
       </c>
       <c r="C72" t="n">
-        <v>12936</v>
+        <v>17582</v>
       </c>
       <c r="D72" t="n">
         <v>10000</v>
       </c>
       <c r="E72" t="n">
-        <v>17582</v>
+        <v>11238</v>
       </c>
       <c r="F72" t="n">
-        <v>15207</v>
+        <v>12936</v>
       </c>
     </row>
     <row r="73">
@@ -8394,19 +8570,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11261</v>
+        <v>15020</v>
       </c>
       <c r="C73" t="n">
-        <v>12712</v>
+        <v>17857</v>
       </c>
       <c r="D73" t="n">
         <v>10000</v>
       </c>
       <c r="E73" t="n">
-        <v>17857</v>
+        <v>11261</v>
       </c>
       <c r="F73" t="n">
-        <v>15020</v>
+        <v>12712</v>
       </c>
     </row>
     <row r="74">
@@ -8416,19 +8592,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>11152</v>
+        <v>15220</v>
       </c>
       <c r="C74" t="n">
-        <v>12712</v>
+        <v>17470</v>
       </c>
       <c r="D74" t="n">
         <v>10323</v>
       </c>
       <c r="E74" t="n">
-        <v>17470</v>
+        <v>11152</v>
       </c>
       <c r="F74" t="n">
-        <v>15220</v>
+        <v>12712</v>
       </c>
     </row>
     <row r="75">
@@ -8438,19 +8614,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11061</v>
+        <v>15585</v>
       </c>
       <c r="C75" t="n">
-        <v>13126</v>
+        <v>17516</v>
       </c>
       <c r="D75" t="n">
         <v>10323</v>
       </c>
       <c r="E75" t="n">
-        <v>17516</v>
+        <v>11061</v>
       </c>
       <c r="F75" t="n">
-        <v>15585</v>
+        <v>13126</v>
       </c>
     </row>
     <row r="76">
@@ -8460,19 +8636,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>11261</v>
+        <v>15835</v>
       </c>
       <c r="C76" t="n">
-        <v>13156</v>
+        <v>17514</v>
       </c>
       <c r="D76" t="n">
         <v>10492</v>
       </c>
       <c r="E76" t="n">
-        <v>17514</v>
+        <v>11261</v>
       </c>
       <c r="F76" t="n">
-        <v>15835</v>
+        <v>13156</v>
       </c>
     </row>
     <row r="77">
@@ -8482,19 +8658,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>11367</v>
+        <v>15066</v>
       </c>
       <c r="C77" t="n">
-        <v>12584</v>
+        <v>17251</v>
       </c>
       <c r="D77" t="n">
         <v>10323</v>
       </c>
       <c r="E77" t="n">
-        <v>17251</v>
+        <v>11367</v>
       </c>
       <c r="F77" t="n">
-        <v>15066</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="78">
@@ -8504,19 +8680,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>10982</v>
+        <v>15075</v>
       </c>
       <c r="C78" t="n">
-        <v>12363</v>
+        <v>17261</v>
       </c>
       <c r="D78" t="n">
         <v>10000</v>
       </c>
       <c r="E78" t="n">
-        <v>17261</v>
+        <v>10982</v>
       </c>
       <c r="F78" t="n">
-        <v>15075</v>
+        <v>12363</v>
       </c>
     </row>
     <row r="79">
@@ -8526,19 +8702,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>10675</v>
+        <v>15214</v>
       </c>
       <c r="C79" t="n">
-        <v>12415</v>
+        <v>17016</v>
       </c>
       <c r="D79" t="n">
         <v>10000</v>
       </c>
       <c r="E79" t="n">
-        <v>17016</v>
+        <v>10675</v>
       </c>
       <c r="F79" t="n">
-        <v>15214</v>
+        <v>12415</v>
       </c>
     </row>
     <row r="80">
@@ -8548,19 +8724,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>11175</v>
+        <v>15275</v>
       </c>
       <c r="C80" t="n">
-        <v>12604</v>
+        <v>17153</v>
       </c>
       <c r="D80" t="n">
         <v>10323</v>
       </c>
       <c r="E80" t="n">
-        <v>17153</v>
+        <v>11175</v>
       </c>
       <c r="F80" t="n">
-        <v>15275</v>
+        <v>12604</v>
       </c>
     </row>
     <row r="81">
@@ -8570,19 +8746,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>10852</v>
+        <v>14873</v>
       </c>
       <c r="C81" t="n">
-        <v>12061</v>
+        <v>16780</v>
       </c>
       <c r="D81" t="n">
         <v>9933</v>
       </c>
       <c r="E81" t="n">
-        <v>16780</v>
+        <v>10852</v>
       </c>
       <c r="F81" t="n">
-        <v>14873</v>
+        <v>12061</v>
       </c>
     </row>
     <row r="82">
@@ -8592,19 +8768,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>10741</v>
+        <v>14710</v>
       </c>
       <c r="C82" t="n">
-        <v>12052</v>
+        <v>16779</v>
       </c>
       <c r="D82" t="n">
         <v>9764</v>
       </c>
       <c r="E82" t="n">
-        <v>16779</v>
+        <v>10741</v>
       </c>
       <c r="F82" t="n">
-        <v>14710</v>
+        <v>12052</v>
       </c>
     </row>
     <row r="83">
@@ -8614,19 +8790,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10356</v>
+        <v>14520</v>
       </c>
       <c r="C83" t="n">
-        <v>11907</v>
+        <v>16585</v>
       </c>
       <c r="D83" t="n">
         <v>9764</v>
       </c>
       <c r="E83" t="n">
-        <v>16585</v>
+        <v>10356</v>
       </c>
       <c r="F83" t="n">
-        <v>14520</v>
+        <v>11907</v>
       </c>
     </row>
     <row r="84">
@@ -8636,19 +8812,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>10068</v>
+        <v>14120</v>
       </c>
       <c r="C84" t="n">
-        <v>11433</v>
+        <v>16431</v>
       </c>
       <c r="D84" t="n">
         <v>9322</v>
       </c>
       <c r="E84" t="n">
-        <v>16431</v>
+        <v>10068</v>
       </c>
       <c r="F84" t="n">
-        <v>14120</v>
+        <v>11433</v>
       </c>
     </row>
     <row r="85">
@@ -8658,19 +8834,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9766</v>
+        <v>13965</v>
       </c>
       <c r="C85" t="n">
-        <v>11180</v>
+        <v>16029</v>
       </c>
       <c r="D85" t="n">
         <v>9146</v>
       </c>
       <c r="E85" t="n">
-        <v>16029</v>
+        <v>9766</v>
       </c>
       <c r="F85" t="n">
-        <v>13965</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="86">
@@ -8680,19 +8856,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9462</v>
+        <v>13884</v>
       </c>
       <c r="C86" t="n">
-        <v>11088</v>
+        <v>15851</v>
       </c>
       <c r="D86" t="n">
         <v>8973</v>
       </c>
       <c r="E86" t="n">
-        <v>15851</v>
+        <v>9462</v>
       </c>
       <c r="F86" t="n">
-        <v>13884</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="87">
@@ -8702,19 +8878,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9571</v>
+        <v>13872</v>
       </c>
       <c r="C87" t="n">
-        <v>11383</v>
+        <v>15701</v>
       </c>
       <c r="D87" t="n">
         <v>9146</v>
       </c>
       <c r="E87" t="n">
-        <v>15701</v>
+        <v>9571</v>
       </c>
       <c r="F87" t="n">
-        <v>13872</v>
+        <v>11383</v>
       </c>
     </row>
     <row r="88">
@@ -8724,19 +8900,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9462</v>
+        <v>13832</v>
       </c>
       <c r="C88" t="n">
-        <v>11274</v>
+        <v>16059</v>
       </c>
       <c r="D88" t="n">
         <v>8794</v>
       </c>
       <c r="E88" t="n">
-        <v>16059</v>
+        <v>9462</v>
       </c>
       <c r="F88" t="n">
-        <v>13832</v>
+        <v>11274</v>
       </c>
     </row>
     <row r="89">
@@ -8746,19 +8922,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9645</v>
+        <v>13666</v>
       </c>
       <c r="C89" t="n">
-        <v>10722</v>
+        <v>15984</v>
       </c>
       <c r="D89" t="n">
         <v>8794</v>
       </c>
       <c r="E89" t="n">
-        <v>15984</v>
+        <v>9645</v>
       </c>
       <c r="F89" t="n">
-        <v>13666</v>
+        <v>10722</v>
       </c>
     </row>
     <row r="90">
@@ -8768,19 +8944,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9641</v>
+        <v>13552</v>
       </c>
       <c r="C90" t="n">
-        <v>10727</v>
+        <v>15685</v>
       </c>
       <c r="D90" t="n">
         <v>8664</v>
       </c>
       <c r="E90" t="n">
-        <v>15685</v>
+        <v>9641</v>
       </c>
       <c r="F90" t="n">
-        <v>13552</v>
+        <v>10727</v>
       </c>
     </row>
     <row r="91">
@@ -8790,19 +8966,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9641</v>
+        <v>13581</v>
       </c>
       <c r="C91" t="n">
-        <v>10496</v>
+        <v>15685</v>
       </c>
       <c r="D91" t="n">
         <v>8664</v>
       </c>
       <c r="E91" t="n">
-        <v>15685</v>
+        <v>9641</v>
       </c>
       <c r="F91" t="n">
-        <v>13581</v>
+        <v>10496</v>
       </c>
     </row>
     <row r="92">
@@ -8812,19 +8988,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>9752</v>
+        <v>13706</v>
       </c>
       <c r="C92" t="n">
-        <v>10405</v>
+        <v>15735</v>
       </c>
       <c r="D92" t="n">
         <v>8664</v>
       </c>
       <c r="E92" t="n">
-        <v>15735</v>
+        <v>9752</v>
       </c>
       <c r="F92" t="n">
-        <v>13706</v>
+        <v>10405</v>
       </c>
     </row>
     <row r="93">
@@ -8834,19 +9010,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9752</v>
+        <v>13615</v>
       </c>
       <c r="C93" t="n">
-        <v>10176</v>
+        <v>15685</v>
       </c>
       <c r="D93" t="n">
         <v>8664</v>
       </c>
       <c r="E93" t="n">
-        <v>15685</v>
+        <v>9752</v>
       </c>
       <c r="F93" t="n">
-        <v>13615</v>
+        <v>10176</v>
       </c>
     </row>
     <row r="94">
@@ -8856,19 +9032,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9641</v>
+        <v>13455</v>
       </c>
       <c r="C94" t="n">
-        <v>10011</v>
+        <v>15590</v>
       </c>
       <c r="D94" t="n">
         <v>7820</v>
       </c>
       <c r="E94" t="n">
-        <v>15590</v>
+        <v>9641</v>
       </c>
       <c r="F94" t="n">
-        <v>13455</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="95">
@@ -8878,19 +9054,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9641</v>
+        <v>13455</v>
       </c>
       <c r="C95" t="n">
-        <v>10111</v>
+        <v>15508</v>
       </c>
       <c r="D95" t="n">
         <v>7820</v>
       </c>
       <c r="E95" t="n">
-        <v>15508</v>
+        <v>9641</v>
       </c>
       <c r="F95" t="n">
-        <v>13455</v>
+        <v>10111</v>
       </c>
     </row>
     <row r="96">
@@ -8900,19 +9076,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9641</v>
+        <v>13426</v>
       </c>
       <c r="C96" t="n">
-        <v>10020</v>
+        <v>15397</v>
       </c>
       <c r="D96" t="n">
         <v>7820</v>
       </c>
       <c r="E96" t="n">
-        <v>15397</v>
+        <v>9641</v>
       </c>
       <c r="F96" t="n">
-        <v>13426</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="97">
@@ -8922,19 +9098,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9352</v>
+        <v>13186</v>
       </c>
       <c r="C97" t="n">
-        <v>9754</v>
+        <v>15391</v>
       </c>
       <c r="D97" t="n">
         <v>7820</v>
       </c>
       <c r="E97" t="n">
-        <v>15391</v>
+        <v>9352</v>
       </c>
       <c r="F97" t="n">
-        <v>13186</v>
+        <v>9754</v>
       </c>
     </row>
     <row r="98">
@@ -8944,19 +9120,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>9352</v>
+        <v>13019</v>
       </c>
       <c r="C98" t="n">
-        <v>9687</v>
+        <v>15348</v>
       </c>
       <c r="D98" t="n">
         <v>7820</v>
       </c>
       <c r="E98" t="n">
-        <v>15348</v>
+        <v>9352</v>
       </c>
       <c r="F98" t="n">
-        <v>13019</v>
+        <v>9687</v>
       </c>
     </row>
     <row r="99">
@@ -8966,19 +9142,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>9352</v>
+        <v>13275</v>
       </c>
       <c r="C99" t="n">
-        <v>9768</v>
+        <v>15425</v>
       </c>
       <c r="D99" t="n">
         <v>7820</v>
       </c>
       <c r="E99" t="n">
-        <v>15425</v>
+        <v>9352</v>
       </c>
       <c r="F99" t="n">
-        <v>13275</v>
+        <v>9768</v>
       </c>
     </row>
     <row r="100">
@@ -8988,19 +9164,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>9459</v>
+        <v>13401</v>
       </c>
       <c r="C100" t="n">
-        <v>9847</v>
+        <v>15462</v>
       </c>
       <c r="D100" t="n">
         <v>8330</v>
       </c>
       <c r="E100" t="n">
-        <v>15462</v>
+        <v>9459</v>
       </c>
       <c r="F100" t="n">
-        <v>13401</v>
+        <v>9847</v>
       </c>
     </row>
     <row r="101">
@@ -9010,19 +9186,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9459</v>
+        <v>13337</v>
       </c>
       <c r="C101" t="n">
-        <v>9643</v>
+        <v>15578</v>
       </c>
       <c r="D101" t="n">
         <v>8153</v>
       </c>
       <c r="E101" t="n">
-        <v>15578</v>
+        <v>9459</v>
       </c>
       <c r="F101" t="n">
-        <v>13337</v>
+        <v>9643</v>
       </c>
     </row>
     <row r="102">
@@ -9032,19 +9208,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>9568</v>
+        <v>13404</v>
       </c>
       <c r="C102" t="n">
-        <v>10047</v>
+        <v>15593</v>
       </c>
       <c r="D102" t="n">
         <v>8153</v>
       </c>
       <c r="E102" t="n">
-        <v>15593</v>
+        <v>9568</v>
       </c>
       <c r="F102" t="n">
-        <v>13404</v>
+        <v>10047</v>
       </c>
     </row>
     <row r="103">
@@ -9054,19 +9230,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>9568</v>
+        <v>13438</v>
       </c>
       <c r="C103" t="n">
-        <v>10144</v>
+        <v>15622</v>
       </c>
       <c r="D103" t="n">
         <v>8153</v>
       </c>
       <c r="E103" t="n">
-        <v>15622</v>
+        <v>9568</v>
       </c>
       <c r="F103" t="n">
-        <v>13438</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="104">
@@ -9076,19 +9252,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9568</v>
+        <v>13586</v>
       </c>
       <c r="C104" t="n">
-        <v>10294</v>
+        <v>15695</v>
       </c>
       <c r="D104" t="n">
         <v>8153</v>
       </c>
       <c r="E104" t="n">
-        <v>15695</v>
+        <v>9568</v>
       </c>
       <c r="F104" t="n">
-        <v>13586</v>
+        <v>10294</v>
       </c>
     </row>
     <row r="105">
@@ -9098,19 +9274,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>13296</v>
+        <v>17385</v>
       </c>
       <c r="C105" t="n">
-        <v>14088</v>
+        <v>19484</v>
       </c>
       <c r="D105" t="n">
         <v>10664</v>
       </c>
       <c r="E105" t="n">
-        <v>19484</v>
+        <v>13296</v>
       </c>
       <c r="F105" t="n">
-        <v>17385</v>
+        <v>14088</v>
       </c>
     </row>
     <row r="106">
@@ -9120,19 +9296,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>9755</v>
+        <v>13385</v>
       </c>
       <c r="C106" t="n">
-        <v>10360</v>
+        <v>15703</v>
       </c>
       <c r="D106" t="n">
         <v>8330</v>
       </c>
       <c r="E106" t="n">
-        <v>15703</v>
+        <v>9755</v>
       </c>
       <c r="F106" t="n">
-        <v>13385</v>
+        <v>10360</v>
       </c>
     </row>
     <row r="107">
@@ -9142,19 +9318,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>9838</v>
+        <v>13440</v>
       </c>
       <c r="C107" t="n">
-        <v>10422</v>
+        <v>15749</v>
       </c>
       <c r="D107" t="n">
         <v>8330</v>
       </c>
       <c r="E107" t="n">
-        <v>15749</v>
+        <v>9838</v>
       </c>
       <c r="F107" t="n">
-        <v>13440</v>
+        <v>10422</v>
       </c>
     </row>
     <row r="108">
@@ -9164,19 +9340,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10439</v>
+        <v>13679</v>
       </c>
       <c r="C108" t="n">
-        <v>10680</v>
+        <v>15969</v>
       </c>
       <c r="D108" t="n">
         <v>8500</v>
       </c>
       <c r="E108" t="n">
-        <v>15969</v>
+        <v>10439</v>
       </c>
       <c r="F108" t="n">
-        <v>13679</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="109">
@@ -9186,19 +9362,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10889</v>
+        <v>13967</v>
       </c>
       <c r="C109" t="n">
-        <v>10986</v>
+        <v>16014</v>
       </c>
       <c r="D109" t="n">
         <v>8830</v>
       </c>
       <c r="E109" t="n">
-        <v>16014</v>
+        <v>10889</v>
       </c>
       <c r="F109" t="n">
-        <v>13967</v>
+        <v>10986</v>
       </c>
     </row>
     <row r="110">
@@ -9208,19 +9384,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11197</v>
+        <v>14289</v>
       </c>
       <c r="C110" t="n">
-        <v>11229</v>
+        <v>16474</v>
       </c>
       <c r="D110" t="n">
         <v>9000</v>
       </c>
       <c r="E110" t="n">
-        <v>16474</v>
+        <v>11197</v>
       </c>
       <c r="F110" t="n">
-        <v>14289</v>
+        <v>11229</v>
       </c>
     </row>
     <row r="111">
@@ -9230,19 +9406,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>12298</v>
+        <v>14480</v>
       </c>
       <c r="C111" t="n">
-        <v>11834</v>
+        <v>16668</v>
       </c>
       <c r="D111" t="n">
         <v>9664</v>
       </c>
       <c r="E111" t="n">
-        <v>16668</v>
+        <v>12298</v>
       </c>
       <c r="F111" t="n">
-        <v>14480</v>
+        <v>11834</v>
       </c>
     </row>
     <row r="112">
@@ -9252,19 +9428,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>12298</v>
+        <v>14480</v>
       </c>
       <c r="C112" t="n">
-        <v>12120</v>
+        <v>16668</v>
       </c>
       <c r="D112" t="n">
         <v>9664</v>
       </c>
       <c r="E112" t="n">
-        <v>16668</v>
+        <v>12298</v>
       </c>
       <c r="F112" t="n">
-        <v>14480</v>
+        <v>12120</v>
       </c>
     </row>
     <row r="113">
@@ -9274,19 +9450,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>12198</v>
+        <v>14819</v>
       </c>
       <c r="C113" t="n">
-        <v>12546</v>
+        <v>16735</v>
       </c>
       <c r="D113" t="n">
         <v>9664</v>
       </c>
       <c r="E113" t="n">
-        <v>16735</v>
+        <v>12198</v>
       </c>
       <c r="F113" t="n">
-        <v>14819</v>
+        <v>12546</v>
       </c>
     </row>
     <row r="114">
@@ -9296,19 +9472,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>11780</v>
+        <v>14973</v>
       </c>
       <c r="C114" t="n">
-        <v>12928</v>
+        <v>16807</v>
       </c>
       <c r="D114" t="n">
         <v>9664</v>
       </c>
       <c r="E114" t="n">
-        <v>16807</v>
+        <v>11780</v>
       </c>
       <c r="F114" t="n">
-        <v>14973</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="115">
@@ -9318,19 +9494,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>12198</v>
+        <v>14982</v>
       </c>
       <c r="C115" t="n">
-        <v>12580</v>
+        <v>16847</v>
       </c>
       <c r="D115" t="n">
         <v>9664</v>
       </c>
       <c r="E115" t="n">
-        <v>16847</v>
+        <v>12198</v>
       </c>
       <c r="F115" t="n">
-        <v>14982</v>
+        <v>12580</v>
       </c>
     </row>
     <row r="116">
@@ -9340,19 +9516,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12298</v>
+        <v>15524</v>
       </c>
       <c r="C116" t="n">
-        <v>13236</v>
+        <v>17634</v>
       </c>
       <c r="D116" t="n">
         <v>9664</v>
       </c>
       <c r="E116" t="n">
-        <v>17634</v>
+        <v>12298</v>
       </c>
       <c r="F116" t="n">
-        <v>15524</v>
+        <v>13236</v>
       </c>
     </row>
     <row r="117">
@@ -9362,19 +9538,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>12500</v>
+        <v>16402</v>
       </c>
       <c r="C117" t="n">
-        <v>14246</v>
+        <v>18421</v>
       </c>
       <c r="D117" t="n">
         <v>10664</v>
       </c>
       <c r="E117" t="n">
-        <v>18421</v>
+        <v>12500</v>
       </c>
       <c r="F117" t="n">
-        <v>16402</v>
+        <v>14246</v>
       </c>
     </row>
     <row r="118">
@@ -9384,19 +9560,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>13567</v>
+        <v>16635</v>
       </c>
       <c r="C118" t="n">
-        <v>13847</v>
+        <v>18653</v>
       </c>
       <c r="D118" t="n">
         <v>10831</v>
       </c>
       <c r="E118" t="n">
-        <v>18653</v>
+        <v>13567</v>
       </c>
       <c r="F118" t="n">
-        <v>16635</v>
+        <v>13847</v>
       </c>
     </row>
     <row r="119">
@@ -9406,19 +9582,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>13109</v>
+        <v>16827</v>
       </c>
       <c r="C119" t="n">
-        <v>13944</v>
+        <v>18984</v>
       </c>
       <c r="D119" t="n">
         <v>10664</v>
       </c>
       <c r="E119" t="n">
-        <v>18984</v>
+        <v>13109</v>
       </c>
       <c r="F119" t="n">
-        <v>16827</v>
+        <v>13944</v>
       </c>
     </row>
     <row r="120">
@@ -9428,19 +9604,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>13296</v>
+        <v>17133</v>
       </c>
       <c r="C120" t="n">
-        <v>14217</v>
+        <v>19319</v>
       </c>
       <c r="D120" t="n">
         <v>10664</v>
       </c>
       <c r="E120" t="n">
-        <v>19319</v>
+        <v>13296</v>
       </c>
       <c r="F120" t="n">
-        <v>17133</v>
+        <v>14217</v>
       </c>
     </row>
     <row r="121">
@@ -9450,19 +9626,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>13296</v>
+        <v>17385</v>
       </c>
       <c r="C121" t="n">
-        <v>14088</v>
+        <v>19484</v>
       </c>
       <c r="D121" t="n">
         <v>10664</v>
       </c>
       <c r="E121" t="n">
-        <v>19484</v>
+        <v>13296</v>
       </c>
       <c r="F121" t="n">
-        <v>17385</v>
+        <v>14088</v>
       </c>
     </row>
     <row r="122">
@@ -9472,19 +9648,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>13547</v>
+        <v>17919</v>
       </c>
       <c r="C122" t="n">
-        <v>14598</v>
+        <v>19982</v>
       </c>
       <c r="D122" t="n">
         <v>10664</v>
       </c>
       <c r="E122" t="n">
-        <v>19982</v>
+        <v>13547</v>
       </c>
       <c r="F122" t="n">
-        <v>17919</v>
+        <v>14598</v>
       </c>
     </row>
     <row r="123">
@@ -9494,19 +9670,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>13547</v>
+        <v>18444</v>
       </c>
       <c r="C123" t="n">
-        <v>15726</v>
+        <v>20351</v>
       </c>
       <c r="D123" t="n">
         <v>11664</v>
       </c>
       <c r="E123" t="n">
-        <v>20351</v>
+        <v>13547</v>
       </c>
       <c r="F123" t="n">
-        <v>18444</v>
+        <v>15726</v>
       </c>
     </row>
     <row r="124">
@@ -9516,19 +9692,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>13547</v>
+        <v>19192</v>
       </c>
       <c r="C124" t="n">
-        <v>16036</v>
+        <v>21500</v>
       </c>
       <c r="D124" t="n">
         <v>11664</v>
       </c>
       <c r="E124" t="n">
-        <v>21500</v>
+        <v>13547</v>
       </c>
       <c r="F124" t="n">
-        <v>19192</v>
+        <v>16036</v>
       </c>
     </row>
     <row r="125">
@@ -9538,19 +9714,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>13981</v>
+        <v>19526</v>
       </c>
       <c r="C125" t="n">
-        <v>16533</v>
+        <v>21852</v>
       </c>
       <c r="D125" t="n">
         <v>12658</v>
       </c>
       <c r="E125" t="n">
-        <v>21852</v>
+        <v>13981</v>
       </c>
       <c r="F125" t="n">
-        <v>19526</v>
+        <v>16533</v>
       </c>
     </row>
     <row r="126">
@@ -9560,19 +9736,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>14902</v>
+        <v>20104</v>
       </c>
       <c r="C126" t="n">
-        <v>16783</v>
+        <v>22264</v>
       </c>
       <c r="D126" t="n">
         <v>12980</v>
       </c>
       <c r="E126" t="n">
-        <v>22264</v>
+        <v>14902</v>
       </c>
       <c r="F126" t="n">
-        <v>20104</v>
+        <v>16783</v>
       </c>
     </row>
     <row r="127">
@@ -9582,19 +9758,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>14182</v>
+        <v>20209</v>
       </c>
       <c r="C127" t="n">
-        <v>16679</v>
+        <v>22633</v>
       </c>
       <c r="D127" t="n">
         <v>12651</v>
       </c>
       <c r="E127" t="n">
-        <v>22633</v>
+        <v>14182</v>
       </c>
       <c r="F127" t="n">
-        <v>20209</v>
+        <v>16679</v>
       </c>
     </row>
     <row r="128">
@@ -9604,19 +9780,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>13883</v>
+        <v>20152</v>
       </c>
       <c r="C128" t="n">
-        <v>16637</v>
+        <v>22610</v>
       </c>
       <c r="D128" t="n">
         <v>12331</v>
       </c>
       <c r="E128" t="n">
-        <v>22610</v>
+        <v>13883</v>
       </c>
       <c r="F128" t="n">
-        <v>20152</v>
+        <v>16637</v>
       </c>
     </row>
     <row r="129">
@@ -9626,19 +9802,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>13349</v>
+        <v>19935</v>
       </c>
       <c r="C129" t="n">
-        <v>16295</v>
+        <v>22193</v>
       </c>
       <c r="D129" t="n">
         <v>11979</v>
       </c>
       <c r="E129" t="n">
-        <v>22193</v>
+        <v>13349</v>
       </c>
       <c r="F129" t="n">
-        <v>19935</v>
+        <v>16295</v>
       </c>
     </row>
     <row r="130">
@@ -9648,19 +9824,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>13453</v>
+        <v>19736</v>
       </c>
       <c r="C130" t="n">
-        <v>16337</v>
+        <v>22115</v>
       </c>
       <c r="D130" t="n">
         <v>11817</v>
       </c>
       <c r="E130" t="n">
-        <v>22115</v>
+        <v>13453</v>
       </c>
       <c r="F130" t="n">
-        <v>19736</v>
+        <v>16337</v>
       </c>
     </row>
     <row r="131">
@@ -9670,19 +9846,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>13453</v>
+        <v>19726</v>
       </c>
       <c r="C131" t="n">
-        <v>15905</v>
+        <v>22115</v>
       </c>
       <c r="D131" t="n">
         <v>11817</v>
       </c>
       <c r="E131" t="n">
-        <v>22115</v>
+        <v>13453</v>
       </c>
       <c r="F131" t="n">
-        <v>19726</v>
+        <v>15905</v>
       </c>
     </row>
     <row r="132">
@@ -9692,19 +9868,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>13043</v>
+        <v>18937</v>
       </c>
       <c r="C132" t="n">
-        <v>15057</v>
+        <v>21649</v>
       </c>
       <c r="D132" t="n">
         <v>11324</v>
       </c>
       <c r="E132" t="n">
-        <v>21649</v>
+        <v>13043</v>
       </c>
       <c r="F132" t="n">
-        <v>18937</v>
+        <v>15057</v>
       </c>
     </row>
     <row r="133">
@@ -9714,19 +9890,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>12361</v>
+        <v>17826</v>
       </c>
       <c r="C133" t="n">
-        <v>13964</v>
+        <v>20845</v>
       </c>
       <c r="D133" t="n">
         <v>9906</v>
       </c>
       <c r="E133" t="n">
-        <v>20845</v>
+        <v>12361</v>
       </c>
       <c r="F133" t="n">
-        <v>17826</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="134">
@@ -9736,19 +9912,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>12559</v>
+        <v>17488</v>
       </c>
       <c r="C134" t="n">
-        <v>13952</v>
+        <v>20475</v>
       </c>
       <c r="D134" t="n">
         <v>9967</v>
       </c>
       <c r="E134" t="n">
-        <v>20475</v>
+        <v>12559</v>
       </c>
       <c r="F134" t="n">
-        <v>17488</v>
+        <v>13952</v>
       </c>
     </row>
     <row r="135">
@@ -9758,19 +9934,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>11874</v>
+        <v>16065</v>
       </c>
       <c r="C135" t="n">
-        <v>13101</v>
+        <v>19003</v>
       </c>
       <c r="D135" t="n">
         <v>9322</v>
       </c>
       <c r="E135" t="n">
-        <v>19003</v>
+        <v>11874</v>
       </c>
       <c r="F135" t="n">
-        <v>16065</v>
+        <v>13101</v>
       </c>
     </row>
     <row r="136">
@@ -9780,19 +9956,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>11874</v>
+        <v>15992</v>
       </c>
       <c r="C136" t="n">
-        <v>13052</v>
+        <v>19014</v>
       </c>
       <c r="D136" t="n">
         <v>9322</v>
       </c>
       <c r="E136" t="n">
-        <v>19014</v>
+        <v>11874</v>
       </c>
       <c r="F136" t="n">
-        <v>15992</v>
+        <v>13052</v>
       </c>
     </row>
     <row r="137">
@@ -9802,19 +9978,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>11088</v>
+        <v>16242</v>
       </c>
       <c r="C137" t="n">
-        <v>12868</v>
+        <v>18814</v>
       </c>
       <c r="D137" t="n">
         <v>9322</v>
       </c>
       <c r="E137" t="n">
-        <v>18814</v>
+        <v>11088</v>
       </c>
       <c r="F137" t="n">
-        <v>16242</v>
+        <v>12868</v>
       </c>
     </row>
     <row r="138">
@@ -9824,19 +10000,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>11016</v>
+        <v>16319</v>
       </c>
       <c r="C138" t="n">
-        <v>12924</v>
+        <v>18894</v>
       </c>
       <c r="D138" t="n">
         <v>9322</v>
       </c>
       <c r="E138" t="n">
-        <v>18894</v>
+        <v>11016</v>
       </c>
       <c r="F138" t="n">
-        <v>16319</v>
+        <v>12924</v>
       </c>
     </row>
     <row r="139">
@@ -9846,19 +10022,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>11016</v>
+        <v>16319</v>
       </c>
       <c r="C139" t="n">
-        <v>12761</v>
+        <v>18668</v>
       </c>
       <c r="D139" t="n">
         <v>9322</v>
       </c>
       <c r="E139" t="n">
-        <v>18668</v>
+        <v>11016</v>
       </c>
       <c r="F139" t="n">
-        <v>16319</v>
+        <v>12761</v>
       </c>
     </row>
     <row r="140">
@@ -9868,19 +10044,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11016</v>
+        <v>16234</v>
       </c>
       <c r="C140" t="n">
-        <v>12614</v>
+        <v>18821</v>
       </c>
       <c r="D140" t="n">
         <v>9322</v>
       </c>
       <c r="E140" t="n">
-        <v>18821</v>
+        <v>11016</v>
       </c>
       <c r="F140" t="n">
-        <v>16234</v>
+        <v>12614</v>
       </c>
     </row>
     <row r="141">
@@ -9890,19 +10066,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11016</v>
+        <v>16234</v>
       </c>
       <c r="C141" t="n">
-        <v>12514</v>
+        <v>18773</v>
       </c>
       <c r="D141" t="n">
         <v>9164</v>
       </c>
       <c r="E141" t="n">
-        <v>18773</v>
+        <v>11016</v>
       </c>
       <c r="F141" t="n">
-        <v>16234</v>
+        <v>12514</v>
       </c>
     </row>
     <row r="142">
@@ -9912,19 +10088,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>11016</v>
+        <v>16193</v>
       </c>
       <c r="C142" t="n">
-        <v>12432</v>
+        <v>18689</v>
       </c>
       <c r="D142" t="n">
         <v>9164</v>
       </c>
       <c r="E142" t="n">
-        <v>18689</v>
+        <v>11016</v>
       </c>
       <c r="F142" t="n">
-        <v>16193</v>
+        <v>12432</v>
       </c>
     </row>
     <row r="143">
@@ -9934,19 +10110,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11016</v>
+        <v>15791</v>
       </c>
       <c r="C143" t="n">
-        <v>12314</v>
+        <v>18387</v>
       </c>
       <c r="D143" t="n">
         <v>9164</v>
       </c>
       <c r="E143" t="n">
-        <v>18387</v>
+        <v>11016</v>
       </c>
       <c r="F143" t="n">
-        <v>15791</v>
+        <v>12314</v>
       </c>
     </row>
     <row r="144">
@@ -9956,19 +10132,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>10751</v>
+        <v>15640</v>
       </c>
       <c r="C144" t="n">
-        <v>11776</v>
+        <v>18258</v>
       </c>
       <c r="D144" t="n">
         <v>9164</v>
       </c>
       <c r="E144" t="n">
-        <v>18258</v>
+        <v>10751</v>
       </c>
       <c r="F144" t="n">
-        <v>15640</v>
+        <v>11776</v>
       </c>
     </row>
     <row r="145">
@@ -9978,19 +10154,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>10700</v>
+        <v>15414</v>
       </c>
       <c r="C145" t="n">
-        <v>11716</v>
+        <v>18003</v>
       </c>
       <c r="D145" t="n">
         <v>9164</v>
       </c>
       <c r="E145" t="n">
-        <v>18003</v>
+        <v>10700</v>
       </c>
       <c r="F145" t="n">
-        <v>15414</v>
+        <v>11716</v>
       </c>
     </row>
     <row r="146">
@@ -10000,19 +10176,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10700</v>
+        <v>15414</v>
       </c>
       <c r="C146" t="n">
-        <v>11810</v>
+        <v>18003</v>
       </c>
       <c r="D146" t="n">
         <v>9164</v>
       </c>
       <c r="E146" t="n">
-        <v>18003</v>
+        <v>10700</v>
       </c>
       <c r="F146" t="n">
-        <v>15414</v>
+        <v>11810</v>
       </c>
     </row>
     <row r="147">
@@ -10022,19 +10198,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>10766</v>
+        <v>15564</v>
       </c>
       <c r="C147" t="n">
-        <v>11911</v>
+        <v>18049</v>
       </c>
       <c r="D147" t="n">
         <v>9000</v>
       </c>
       <c r="E147" t="n">
-        <v>18049</v>
+        <v>10766</v>
       </c>
       <c r="F147" t="n">
-        <v>15564</v>
+        <v>11911</v>
       </c>
     </row>
     <row r="148">
@@ -10044,19 +10220,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10917</v>
+        <v>15453</v>
       </c>
       <c r="C148" t="n">
-        <v>11890</v>
+        <v>18034</v>
       </c>
       <c r="D148" t="n">
         <v>9000</v>
       </c>
       <c r="E148" t="n">
-        <v>18034</v>
+        <v>10917</v>
       </c>
       <c r="F148" t="n">
-        <v>15453</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="149">
@@ -10066,19 +10242,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>10917</v>
+        <v>15595</v>
       </c>
       <c r="C149" t="n">
-        <v>11767</v>
+        <v>18057</v>
       </c>
       <c r="D149" t="n">
         <v>9000</v>
       </c>
       <c r="E149" t="n">
-        <v>18057</v>
+        <v>10917</v>
       </c>
       <c r="F149" t="n">
-        <v>15595</v>
+        <v>11767</v>
       </c>
     </row>
     <row r="150">
@@ -10088,19 +10264,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>10917</v>
+        <v>15554</v>
       </c>
       <c r="C150" t="n">
-        <v>11767</v>
+        <v>17989</v>
       </c>
       <c r="D150" t="n">
         <v>9000</v>
       </c>
       <c r="E150" t="n">
-        <v>17989</v>
+        <v>10917</v>
       </c>
       <c r="F150" t="n">
-        <v>15554</v>
+        <v>11767</v>
       </c>
     </row>
     <row r="151">
@@ -10110,19 +10286,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>10917</v>
+        <v>15462</v>
       </c>
       <c r="C151" t="n">
-        <v>11839</v>
+        <v>18116</v>
       </c>
       <c r="D151" t="n">
         <v>9000</v>
       </c>
       <c r="E151" t="n">
-        <v>18116</v>
+        <v>10917</v>
       </c>
       <c r="F151" t="n">
-        <v>15462</v>
+        <v>11839</v>
       </c>
     </row>
     <row r="152">
@@ -10132,19 +10308,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>10917</v>
+        <v>15579</v>
       </c>
       <c r="C152" t="n">
-        <v>11941</v>
+        <v>18216</v>
       </c>
       <c r="D152" t="n">
         <v>9000</v>
       </c>
       <c r="E152" t="n">
-        <v>18216</v>
+        <v>10917</v>
       </c>
       <c r="F152" t="n">
-        <v>15579</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="153">
@@ -10154,19 +10330,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>11297</v>
+        <v>16070</v>
       </c>
       <c r="C153" t="n">
-        <v>12152</v>
+        <v>18223</v>
       </c>
       <c r="D153" t="n">
         <v>9000</v>
       </c>
       <c r="E153" t="n">
-        <v>18223</v>
+        <v>11297</v>
       </c>
       <c r="F153" t="n">
-        <v>16070</v>
+        <v>12152</v>
       </c>
     </row>
     <row r="154">
@@ -10176,19 +10352,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>11737</v>
+        <v>16271</v>
       </c>
       <c r="C154" t="n">
-        <v>12385</v>
+        <v>18317</v>
       </c>
       <c r="D154" t="n">
         <v>9664</v>
       </c>
       <c r="E154" t="n">
-        <v>18317</v>
+        <v>11737</v>
       </c>
       <c r="F154" t="n">
-        <v>16271</v>
+        <v>12385</v>
       </c>
     </row>
     <row r="155">
@@ -10198,19 +10374,19 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>11993</v>
+        <v>16346</v>
       </c>
       <c r="C155" t="n">
-        <v>12605</v>
+        <v>18277</v>
       </c>
       <c r="D155" t="n">
         <v>9664</v>
       </c>
       <c r="E155" t="n">
-        <v>18277</v>
+        <v>11993</v>
       </c>
       <c r="F155" t="n">
-        <v>16346</v>
+        <v>12605</v>
       </c>
     </row>
     <row r="156">
@@ -10220,19 +10396,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>12157</v>
+        <v>16297</v>
       </c>
       <c r="C156" t="n">
-        <v>12739</v>
+        <v>18595</v>
       </c>
       <c r="D156" t="n">
         <v>9664</v>
       </c>
       <c r="E156" t="n">
-        <v>18595</v>
+        <v>12157</v>
       </c>
       <c r="F156" t="n">
-        <v>16297</v>
+        <v>12739</v>
       </c>
     </row>
     <row r="157">
@@ -10242,19 +10418,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>12147</v>
+        <v>16309</v>
       </c>
       <c r="C157" t="n">
-        <v>12845</v>
+        <v>18660</v>
       </c>
       <c r="D157" t="n">
         <v>9664</v>
       </c>
       <c r="E157" t="n">
-        <v>18660</v>
+        <v>12147</v>
       </c>
       <c r="F157" t="n">
-        <v>16309</v>
+        <v>12845</v>
       </c>
     </row>
     <row r="158">
@@ -10264,19 +10440,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>12057</v>
+        <v>16465</v>
       </c>
       <c r="C158" t="n">
-        <v>13180</v>
+        <v>18679</v>
       </c>
       <c r="D158" t="n">
         <v>9664</v>
       </c>
       <c r="E158" t="n">
-        <v>18679</v>
+        <v>12057</v>
       </c>
       <c r="F158" t="n">
-        <v>16465</v>
+        <v>13180</v>
       </c>
     </row>
     <row r="159">
@@ -10286,19 +10462,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>12133</v>
+        <v>16768</v>
       </c>
       <c r="C159" t="n">
-        <v>13259</v>
+        <v>18836</v>
       </c>
       <c r="D159" t="n">
         <v>9664</v>
       </c>
       <c r="E159" t="n">
-        <v>18836</v>
+        <v>12133</v>
       </c>
       <c r="F159" t="n">
-        <v>16768</v>
+        <v>13259</v>
       </c>
     </row>
     <row r="160">
@@ -10308,19 +10484,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>12133</v>
+        <v>17091</v>
       </c>
       <c r="C160" t="n">
-        <v>13788</v>
+        <v>19225</v>
       </c>
       <c r="D160" t="n">
         <v>9664</v>
       </c>
       <c r="E160" t="n">
-        <v>19225</v>
+        <v>12133</v>
       </c>
       <c r="F160" t="n">
-        <v>17091</v>
+        <v>13788</v>
       </c>
     </row>
     <row r="161">
@@ -10330,19 +10506,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>11906</v>
+        <v>17105</v>
       </c>
       <c r="C161" t="n">
-        <v>13688</v>
+        <v>19224</v>
       </c>
       <c r="D161" t="n">
         <v>9322</v>
       </c>
       <c r="E161" t="n">
-        <v>19224</v>
+        <v>11906</v>
       </c>
       <c r="F161" t="n">
-        <v>17105</v>
+        <v>13688</v>
       </c>
     </row>
     <row r="162">
@@ -10352,19 +10528,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>12290</v>
+        <v>17254</v>
       </c>
       <c r="C162" t="n">
-        <v>13852</v>
+        <v>19170</v>
       </c>
       <c r="D162" t="n">
         <v>9664</v>
       </c>
       <c r="E162" t="n">
-        <v>19170</v>
+        <v>12290</v>
       </c>
       <c r="F162" t="n">
-        <v>17254</v>
+        <v>13852</v>
       </c>
     </row>
     <row r="163">
@@ -10374,19 +10550,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>12290</v>
+        <v>17445</v>
       </c>
       <c r="C163" t="n">
-        <v>13966</v>
+        <v>19528</v>
       </c>
       <c r="D163" t="n">
         <v>9664</v>
       </c>
       <c r="E163" t="n">
-        <v>19528</v>
+        <v>12290</v>
       </c>
       <c r="F163" t="n">
-        <v>17445</v>
+        <v>13966</v>
       </c>
     </row>
     <row r="164">
@@ -10396,19 +10572,19 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>12290</v>
+        <v>17655</v>
       </c>
       <c r="C164" t="n">
-        <v>13933</v>
+        <v>19642</v>
       </c>
       <c r="D164" t="n">
         <v>9664</v>
       </c>
       <c r="E164" t="n">
-        <v>19642</v>
+        <v>12290</v>
       </c>
       <c r="F164" t="n">
-        <v>17655</v>
+        <v>13933</v>
       </c>
     </row>
     <row r="165">
@@ -10418,19 +10594,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>12290</v>
+        <v>17565</v>
       </c>
       <c r="C165" t="n">
-        <v>13902</v>
+        <v>19743</v>
       </c>
       <c r="D165" t="n">
         <v>9664</v>
       </c>
       <c r="E165" t="n">
-        <v>19743</v>
+        <v>12290</v>
       </c>
       <c r="F165" t="n">
-        <v>17565</v>
+        <v>13902</v>
       </c>
     </row>
     <row r="166">
@@ -10440,19 +10616,19 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>12734</v>
+        <v>17831</v>
       </c>
       <c r="C166" t="n">
-        <v>13867</v>
+        <v>19780</v>
       </c>
       <c r="D166" t="n">
         <v>9664</v>
       </c>
       <c r="E166" t="n">
-        <v>19780</v>
+        <v>12734</v>
       </c>
       <c r="F166" t="n">
-        <v>17831</v>
+        <v>13867</v>
       </c>
     </row>
     <row r="167">
@@ -10462,19 +10638,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>13076</v>
+        <v>17897</v>
       </c>
       <c r="C167" t="n">
-        <v>14257</v>
+        <v>19753</v>
       </c>
       <c r="D167" t="n">
         <v>9664</v>
       </c>
       <c r="E167" t="n">
-        <v>19753</v>
+        <v>13076</v>
       </c>
       <c r="F167" t="n">
-        <v>17897</v>
+        <v>14257</v>
       </c>
     </row>
     <row r="168">
@@ -10484,19 +10660,19 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>13331</v>
+        <v>18036</v>
       </c>
       <c r="C168" t="n">
-        <v>14385</v>
+        <v>19881</v>
       </c>
       <c r="D168" t="n">
         <v>10656</v>
       </c>
       <c r="E168" t="n">
-        <v>19881</v>
+        <v>13331</v>
       </c>
       <c r="F168" t="n">
-        <v>18036</v>
+        <v>14385</v>
       </c>
     </row>
     <row r="169">
@@ -10506,19 +10682,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>13978</v>
+        <v>18122</v>
       </c>
       <c r="C169" t="n">
-        <v>14563</v>
+        <v>19997</v>
       </c>
       <c r="D169" t="n">
         <v>10323</v>
       </c>
       <c r="E169" t="n">
-        <v>19997</v>
+        <v>13978</v>
       </c>
       <c r="F169" t="n">
-        <v>18122</v>
+        <v>14563</v>
       </c>
     </row>
     <row r="170">
@@ -10528,19 +10704,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>13701</v>
+        <v>18123</v>
       </c>
       <c r="C170" t="n">
-        <v>14628</v>
+        <v>20174</v>
       </c>
       <c r="D170" t="n">
         <v>10656</v>
       </c>
       <c r="E170" t="n">
-        <v>20174</v>
+        <v>13701</v>
       </c>
       <c r="F170" t="n">
-        <v>18123</v>
+        <v>14628</v>
       </c>
     </row>
     <row r="171">
@@ -10550,19 +10726,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>13931</v>
+        <v>18865</v>
       </c>
       <c r="C171" t="n">
-        <v>15328</v>
+        <v>20277</v>
       </c>
       <c r="D171" t="n">
         <v>10656</v>
       </c>
       <c r="E171" t="n">
-        <v>20277</v>
+        <v>13931</v>
       </c>
       <c r="F171" t="n">
-        <v>18865</v>
+        <v>15328</v>
       </c>
     </row>
     <row r="172">
@@ -10572,19 +10748,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>13932</v>
+        <v>19081</v>
       </c>
       <c r="C172" t="n">
-        <v>15474</v>
+        <v>21230</v>
       </c>
       <c r="D172" t="n">
         <v>10475</v>
       </c>
       <c r="E172" t="n">
-        <v>21230</v>
+        <v>13932</v>
       </c>
       <c r="F172" t="n">
-        <v>19081</v>
+        <v>15474</v>
       </c>
     </row>
     <row r="173">
@@ -10594,19 +10770,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13692</v>
+        <v>19599</v>
       </c>
       <c r="C173" t="n">
-        <v>15802</v>
+        <v>21446</v>
       </c>
       <c r="D173" t="n">
         <v>10475</v>
       </c>
       <c r="E173" t="n">
-        <v>21446</v>
+        <v>13692</v>
       </c>
       <c r="F173" t="n">
-        <v>19599</v>
+        <v>15802</v>
       </c>
     </row>
     <row r="174">
@@ -10616,19 +10792,19 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>13692</v>
+        <v>19730</v>
       </c>
       <c r="C174" t="n">
-        <v>16409</v>
+        <v>21488</v>
       </c>
       <c r="D174" t="n">
         <v>10475</v>
       </c>
       <c r="E174" t="n">
-        <v>21488</v>
+        <v>13692</v>
       </c>
       <c r="F174" t="n">
-        <v>19730</v>
+        <v>16409</v>
       </c>
     </row>
     <row r="175">
@@ -10638,19 +10814,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>14362</v>
+        <v>19723</v>
       </c>
       <c r="C175" t="n">
-        <v>16556</v>
+        <v>21469</v>
       </c>
       <c r="D175" t="n">
         <v>10475</v>
       </c>
       <c r="E175" t="n">
-        <v>21469</v>
+        <v>14362</v>
       </c>
       <c r="F175" t="n">
-        <v>19723</v>
+        <v>16556</v>
       </c>
     </row>
     <row r="176">
@@ -10660,19 +10836,19 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>14562</v>
+        <v>19625</v>
       </c>
       <c r="C176" t="n">
-        <v>16838</v>
+        <v>21626</v>
       </c>
       <c r="D176" t="n">
         <v>10475</v>
       </c>
       <c r="E176" t="n">
-        <v>21626</v>
+        <v>14562</v>
       </c>
       <c r="F176" t="n">
-        <v>19625</v>
+        <v>16838</v>
       </c>
     </row>
     <row r="177">
@@ -10682,19 +10858,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>14191</v>
+        <v>19675</v>
       </c>
       <c r="C177" t="n">
-        <v>16711</v>
+        <v>21640</v>
       </c>
       <c r="D177" t="n">
         <v>10314</v>
       </c>
       <c r="E177" t="n">
-        <v>21640</v>
+        <v>14191</v>
       </c>
       <c r="F177" t="n">
-        <v>19675</v>
+        <v>16711</v>
       </c>
     </row>
     <row r="178">
@@ -10704,19 +10880,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>13790</v>
+        <v>18273</v>
       </c>
       <c r="C178" t="n">
-        <v>16008</v>
+        <v>20549</v>
       </c>
       <c r="D178" t="n">
         <v>10314</v>
       </c>
       <c r="E178" t="n">
-        <v>20549</v>
+        <v>13790</v>
       </c>
       <c r="F178" t="n">
-        <v>18273</v>
+        <v>16008</v>
       </c>
     </row>
     <row r="179">
@@ -10726,19 +10902,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>13996</v>
+        <v>18064</v>
       </c>
       <c r="C179" t="n">
-        <v>15885</v>
+        <v>20239</v>
       </c>
       <c r="D179" t="n">
         <v>10080</v>
       </c>
       <c r="E179" t="n">
-        <v>20239</v>
+        <v>13996</v>
       </c>
       <c r="F179" t="n">
-        <v>18064</v>
+        <v>15885</v>
       </c>
     </row>
     <row r="180">
@@ -10748,19 +10924,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13601</v>
+        <v>18485</v>
       </c>
       <c r="C180" t="n">
-        <v>15582</v>
+        <v>20561</v>
       </c>
       <c r="D180" t="n">
         <v>9976</v>
       </c>
       <c r="E180" t="n">
-        <v>20561</v>
+        <v>13601</v>
       </c>
       <c r="F180" t="n">
-        <v>18485</v>
+        <v>15582</v>
       </c>
     </row>
     <row r="181">
@@ -10770,19 +10946,19 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>13620</v>
+        <v>18722</v>
       </c>
       <c r="C181" t="n">
-        <v>15409</v>
+        <v>20660</v>
       </c>
       <c r="D181" t="n">
         <v>9967</v>
       </c>
       <c r="E181" t="n">
-        <v>20660</v>
+        <v>13620</v>
       </c>
       <c r="F181" t="n">
-        <v>18722</v>
+        <v>15409</v>
       </c>
     </row>
     <row r="182">
@@ -10792,19 +10968,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>13385</v>
+        <v>18611</v>
       </c>
       <c r="C182" t="n">
-        <v>15276</v>
+        <v>20717</v>
       </c>
       <c r="D182" t="n">
         <v>10323</v>
       </c>
       <c r="E182" t="n">
-        <v>20717</v>
+        <v>13385</v>
       </c>
       <c r="F182" t="n">
-        <v>18611</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="183">
@@ -10814,19 +10990,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>13385</v>
+        <v>18318</v>
       </c>
       <c r="C183" t="n">
-        <v>14917</v>
+        <v>20589</v>
       </c>
       <c r="D183" t="n">
         <v>10323</v>
       </c>
       <c r="E183" t="n">
-        <v>20589</v>
+        <v>13385</v>
       </c>
       <c r="F183" t="n">
-        <v>18318</v>
+        <v>14917</v>
       </c>
     </row>
     <row r="184">
@@ -10836,19 +11012,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>13550</v>
+        <v>17920</v>
       </c>
       <c r="C184" t="n">
-        <v>14984</v>
+        <v>20733</v>
       </c>
       <c r="D184" t="n">
         <v>10815</v>
       </c>
       <c r="E184" t="n">
-        <v>20733</v>
+        <v>13550</v>
       </c>
       <c r="F184" t="n">
-        <v>17920</v>
+        <v>14984</v>
       </c>
     </row>
     <row r="185">
@@ -10858,19 +11034,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>12958</v>
+        <v>17787</v>
       </c>
       <c r="C185" t="n">
-        <v>14934</v>
+        <v>20434</v>
       </c>
       <c r="D185" t="n">
         <v>10492</v>
       </c>
       <c r="E185" t="n">
-        <v>20434</v>
+        <v>12958</v>
       </c>
       <c r="F185" t="n">
-        <v>17787</v>
+        <v>14934</v>
       </c>
     </row>
     <row r="186">
@@ -10880,19 +11056,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>12735</v>
+        <v>17513</v>
       </c>
       <c r="C186" t="n">
-        <v>14616</v>
+        <v>20295</v>
       </c>
       <c r="D186" t="n">
         <v>10664</v>
       </c>
       <c r="E186" t="n">
-        <v>20295</v>
+        <v>12735</v>
       </c>
       <c r="F186" t="n">
-        <v>17513</v>
+        <v>14616</v>
       </c>
     </row>
     <row r="187">
@@ -10902,19 +11078,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>12181</v>
+        <v>17721</v>
       </c>
       <c r="C187" t="n">
-        <v>14451</v>
+        <v>20253</v>
       </c>
       <c r="D187" t="n">
         <v>10492</v>
       </c>
       <c r="E187" t="n">
-        <v>20253</v>
+        <v>12181</v>
       </c>
       <c r="F187" t="n">
-        <v>17721</v>
+        <v>14451</v>
       </c>
     </row>
     <row r="188">
@@ -10924,19 +11100,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>12633</v>
+        <v>17931</v>
       </c>
       <c r="C188" t="n">
-        <v>14408</v>
+        <v>20439</v>
       </c>
       <c r="D188" t="n">
         <v>10492</v>
       </c>
       <c r="E188" t="n">
-        <v>20439</v>
+        <v>12633</v>
       </c>
       <c r="F188" t="n">
-        <v>17931</v>
+        <v>14408</v>
       </c>
     </row>
     <row r="189">
@@ -10946,19 +11122,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12526</v>
+        <v>18188</v>
       </c>
       <c r="C189" t="n">
-        <v>14496</v>
+        <v>20689</v>
       </c>
       <c r="D189" t="n">
         <v>10323</v>
       </c>
       <c r="E189" t="n">
-        <v>20689</v>
+        <v>12526</v>
       </c>
       <c r="F189" t="n">
-        <v>18188</v>
+        <v>14496</v>
       </c>
     </row>
     <row r="190">
@@ -10968,19 +11144,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>12526</v>
+        <v>18241</v>
       </c>
       <c r="C190" t="n">
-        <v>14594</v>
+        <v>20689</v>
       </c>
       <c r="D190" t="n">
         <v>10323</v>
       </c>
       <c r="E190" t="n">
-        <v>20689</v>
+        <v>12526</v>
       </c>
       <c r="F190" t="n">
-        <v>18241</v>
+        <v>14594</v>
       </c>
     </row>
     <row r="191">
@@ -10990,19 +11166,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>12526</v>
+        <v>18188</v>
       </c>
       <c r="C191" t="n">
-        <v>14603</v>
+        <v>20599</v>
       </c>
       <c r="D191" t="n">
         <v>10323</v>
       </c>
       <c r="E191" t="n">
-        <v>20599</v>
+        <v>12526</v>
       </c>
       <c r="F191" t="n">
-        <v>18188</v>
+        <v>14603</v>
       </c>
     </row>
     <row r="192">
@@ -11012,19 +11188,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>12526</v>
+        <v>18141</v>
       </c>
       <c r="C192" t="n">
-        <v>14448</v>
+        <v>20594</v>
       </c>
       <c r="D192" t="n">
         <v>10323</v>
       </c>
       <c r="E192" t="n">
-        <v>20594</v>
+        <v>12526</v>
       </c>
       <c r="F192" t="n">
-        <v>18141</v>
+        <v>14448</v>
       </c>
     </row>
     <row r="193">
@@ -11034,19 +11210,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>12415</v>
+        <v>18039</v>
       </c>
       <c r="C193" t="n">
-        <v>14281</v>
+        <v>20421</v>
       </c>
       <c r="D193" t="n">
         <v>10970</v>
       </c>
       <c r="E193" t="n">
-        <v>20421</v>
+        <v>12415</v>
       </c>
       <c r="F193" t="n">
-        <v>18039</v>
+        <v>14281</v>
       </c>
     </row>
     <row r="194">
@@ -11056,19 +11232,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>12415</v>
+        <v>17984</v>
       </c>
       <c r="C194" t="n">
-        <v>14287</v>
+        <v>20443</v>
       </c>
       <c r="D194" t="n">
         <v>10970</v>
       </c>
       <c r="E194" t="n">
-        <v>20443</v>
+        <v>12415</v>
       </c>
       <c r="F194" t="n">
-        <v>17984</v>
+        <v>14287</v>
       </c>
     </row>
     <row r="195">
@@ -11078,19 +11254,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>12526</v>
+        <v>17727</v>
       </c>
       <c r="C195" t="n">
-        <v>14255</v>
+        <v>20334</v>
       </c>
       <c r="D195" t="n">
         <v>10970</v>
       </c>
       <c r="E195" t="n">
-        <v>20334</v>
+        <v>12526</v>
       </c>
       <c r="F195" t="n">
-        <v>17727</v>
+        <v>14255</v>
       </c>
     </row>
     <row r="196">
@@ -11100,19 +11276,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>12300</v>
+        <v>17711</v>
       </c>
       <c r="C196" t="n">
-        <v>14159</v>
+        <v>20334</v>
       </c>
       <c r="D196" t="n">
         <v>10656</v>
       </c>
       <c r="E196" t="n">
-        <v>20334</v>
+        <v>12300</v>
       </c>
       <c r="F196" t="n">
-        <v>17711</v>
+        <v>14159</v>
       </c>
     </row>
     <row r="197">
@@ -11122,19 +11298,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>12068</v>
+        <v>17736</v>
       </c>
       <c r="C197" t="n">
-        <v>14093</v>
+        <v>20446</v>
       </c>
       <c r="D197" t="n">
         <v>10656</v>
       </c>
       <c r="E197" t="n">
-        <v>20446</v>
+        <v>12068</v>
       </c>
       <c r="F197" t="n">
-        <v>17736</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="198">
@@ -11144,19 +11320,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>11951</v>
+        <v>17762</v>
       </c>
       <c r="C198" t="n">
-        <v>14093</v>
+        <v>20408</v>
       </c>
       <c r="D198" t="n">
         <v>10656</v>
       </c>
       <c r="E198" t="n">
-        <v>20408</v>
+        <v>11951</v>
       </c>
       <c r="F198" t="n">
-        <v>17762</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="199">
@@ -11166,19 +11342,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>11951</v>
+        <v>17899</v>
       </c>
       <c r="C199" t="n">
-        <v>14168</v>
+        <v>20264</v>
       </c>
       <c r="D199" t="n">
         <v>10656</v>
       </c>
       <c r="E199" t="n">
-        <v>20264</v>
+        <v>11951</v>
       </c>
       <c r="F199" t="n">
-        <v>17899</v>
+        <v>14168</v>
       </c>
     </row>
     <row r="200">
@@ -11188,19 +11364,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12068</v>
+        <v>17735</v>
       </c>
       <c r="C200" t="n">
-        <v>13998</v>
+        <v>20312</v>
       </c>
       <c r="D200" t="n">
         <v>10656</v>
       </c>
       <c r="E200" t="n">
-        <v>20312</v>
+        <v>12068</v>
       </c>
       <c r="F200" t="n">
-        <v>17735</v>
+        <v>13998</v>
       </c>
     </row>
     <row r="201">
@@ -11210,19 +11386,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11816</v>
+        <v>18068</v>
       </c>
       <c r="C201" t="n">
-        <v>14282</v>
+        <v>20449</v>
       </c>
       <c r="D201" t="n">
         <v>10475</v>
       </c>
       <c r="E201" t="n">
-        <v>20449</v>
+        <v>11816</v>
       </c>
       <c r="F201" t="n">
-        <v>18068</v>
+        <v>14282</v>
       </c>
     </row>
     <row r="202">
@@ -11232,19 +11408,19 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>11945</v>
+        <v>17971</v>
       </c>
       <c r="C202" t="n">
-        <v>14442</v>
+        <v>20492</v>
       </c>
       <c r="D202" t="n">
         <v>10475</v>
       </c>
       <c r="E202" t="n">
-        <v>20492</v>
+        <v>11945</v>
       </c>
       <c r="F202" t="n">
-        <v>17971</v>
+        <v>14442</v>
       </c>
     </row>
     <row r="203">
@@ -11254,19 +11430,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>11829</v>
+        <v>17919</v>
       </c>
       <c r="C203" t="n">
-        <v>14581</v>
+        <v>20399</v>
       </c>
       <c r="D203" t="n">
         <v>10632</v>
       </c>
       <c r="E203" t="n">
-        <v>20399</v>
+        <v>11829</v>
       </c>
       <c r="F203" t="n">
-        <v>17919</v>
+        <v>14581</v>
       </c>
     </row>
     <row r="204">
@@ -11276,19 +11452,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12347</v>
+        <v>18450</v>
       </c>
       <c r="C204" t="n">
-        <v>14989</v>
+        <v>20904</v>
       </c>
       <c r="D204" t="n">
         <v>11101</v>
       </c>
       <c r="E204" t="n">
-        <v>20904</v>
+        <v>12347</v>
       </c>
       <c r="F204" t="n">
-        <v>18450</v>
+        <v>14989</v>
       </c>
     </row>
     <row r="205">
@@ -11298,19 +11474,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>12604</v>
+        <v>18914</v>
       </c>
       <c r="C205" t="n">
-        <v>15211</v>
+        <v>21099</v>
       </c>
       <c r="D205" t="n">
         <v>11101</v>
       </c>
       <c r="E205" t="n">
-        <v>21099</v>
+        <v>12604</v>
       </c>
       <c r="F205" t="n">
-        <v>18914</v>
+        <v>15211</v>
       </c>
     </row>
     <row r="206">
@@ -11320,19 +11496,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>12775</v>
+        <v>18991</v>
       </c>
       <c r="C206" t="n">
-        <v>15276</v>
+        <v>21099</v>
       </c>
       <c r="D206" t="n">
         <v>11253</v>
       </c>
       <c r="E206" t="n">
-        <v>21099</v>
+        <v>12775</v>
       </c>
       <c r="F206" t="n">
-        <v>18991</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="207">
@@ -11342,19 +11518,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>13052</v>
+        <v>19073</v>
       </c>
       <c r="C207" t="n">
-        <v>15490</v>
+        <v>21687</v>
       </c>
       <c r="D207" t="n">
         <v>11253</v>
       </c>
       <c r="E207" t="n">
-        <v>21687</v>
+        <v>13052</v>
       </c>
       <c r="F207" t="n">
-        <v>19073</v>
+        <v>15490</v>
       </c>
     </row>
     <row r="208">
@@ -11364,19 +11540,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>12752</v>
+        <v>19008</v>
       </c>
       <c r="C208" t="n">
-        <v>15642</v>
+        <v>21880</v>
       </c>
       <c r="D208" t="n">
         <v>11253</v>
       </c>
       <c r="E208" t="n">
-        <v>21880</v>
+        <v>12752</v>
       </c>
       <c r="F208" t="n">
-        <v>19008</v>
+        <v>15642</v>
       </c>
     </row>
     <row r="209">
@@ -11386,19 +11562,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>13009</v>
+        <v>19220</v>
       </c>
       <c r="C209" t="n">
-        <v>15836</v>
+        <v>21876</v>
       </c>
       <c r="D209" t="n">
         <v>11253</v>
       </c>
       <c r="E209" t="n">
-        <v>21876</v>
+        <v>13009</v>
       </c>
       <c r="F209" t="n">
-        <v>19220</v>
+        <v>15836</v>
       </c>
     </row>
     <row r="210">
@@ -11408,19 +11584,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>13246</v>
+        <v>19450</v>
       </c>
       <c r="C210" t="n">
-        <v>16153</v>
+        <v>22223</v>
       </c>
       <c r="D210" t="n">
         <v>11253</v>
       </c>
       <c r="E210" t="n">
-        <v>22223</v>
+        <v>13246</v>
       </c>
       <c r="F210" t="n">
-        <v>19450</v>
+        <v>16153</v>
       </c>
     </row>
     <row r="211">
@@ -11430,19 +11606,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>13331</v>
+        <v>19598</v>
       </c>
       <c r="C211" t="n">
-        <v>16523</v>
+        <v>22585</v>
       </c>
       <c r="D211" t="n">
         <v>11253</v>
       </c>
       <c r="E211" t="n">
-        <v>22585</v>
+        <v>13331</v>
       </c>
       <c r="F211" t="n">
-        <v>19598</v>
+        <v>16523</v>
       </c>
     </row>
     <row r="212">
@@ -11452,19 +11628,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>13246</v>
+        <v>19680</v>
       </c>
       <c r="C212" t="n">
-        <v>16511</v>
+        <v>22570</v>
       </c>
       <c r="D212" t="n">
         <v>11253</v>
       </c>
       <c r="E212" t="n">
-        <v>22570</v>
+        <v>13246</v>
       </c>
       <c r="F212" t="n">
-        <v>19680</v>
+        <v>16511</v>
       </c>
     </row>
     <row r="213">
@@ -11474,19 +11650,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>13405</v>
+        <v>19820</v>
       </c>
       <c r="C213" t="n">
-        <v>16802</v>
+        <v>22653</v>
       </c>
       <c r="D213" t="n">
         <v>11447</v>
       </c>
       <c r="E213" t="n">
-        <v>22653</v>
+        <v>13405</v>
       </c>
       <c r="F213" t="n">
-        <v>19820</v>
+        <v>16802</v>
       </c>
     </row>
     <row r="214">
@@ -11496,19 +11672,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>13394</v>
+        <v>19992</v>
       </c>
       <c r="C214" t="n">
-        <v>16981</v>
+        <v>22666</v>
       </c>
       <c r="D214" t="n">
         <v>11133</v>
       </c>
       <c r="E214" t="n">
-        <v>22666</v>
+        <v>13394</v>
       </c>
       <c r="F214" t="n">
-        <v>19992</v>
+        <v>16981</v>
       </c>
     </row>
     <row r="215">
@@ -11518,19 +11694,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>13394</v>
+        <v>19931</v>
       </c>
       <c r="C215" t="n">
-        <v>17115</v>
+        <v>22632</v>
       </c>
       <c r="D215" t="n">
         <v>11133</v>
       </c>
       <c r="E215" t="n">
-        <v>22632</v>
+        <v>13394</v>
       </c>
       <c r="F215" t="n">
-        <v>19931</v>
+        <v>17115</v>
       </c>
     </row>
     <row r="216">
@@ -11540,19 +11716,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>13950</v>
+        <v>19887</v>
       </c>
       <c r="C216" t="n">
-        <v>17263</v>
+        <v>22438</v>
       </c>
       <c r="D216" t="n">
         <v>11831</v>
       </c>
       <c r="E216" t="n">
-        <v>22438</v>
+        <v>13950</v>
       </c>
       <c r="F216" t="n">
-        <v>19887</v>
+        <v>17263</v>
       </c>
     </row>
     <row r="217">
@@ -11562,19 +11738,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>13792</v>
+        <v>19919</v>
       </c>
       <c r="C217" t="n">
-        <v>17351</v>
+        <v>22394</v>
       </c>
       <c r="D217" t="n">
         <v>11831</v>
       </c>
       <c r="E217" t="n">
-        <v>22394</v>
+        <v>13792</v>
       </c>
       <c r="F217" t="n">
-        <v>19919</v>
+        <v>17351</v>
       </c>
     </row>
     <row r="218">
@@ -11584,19 +11760,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>13792</v>
+        <v>19911</v>
       </c>
       <c r="C218" t="n">
-        <v>17375</v>
+        <v>22628</v>
       </c>
       <c r="D218" t="n">
         <v>11831</v>
       </c>
       <c r="E218" t="n">
-        <v>22628</v>
+        <v>13792</v>
       </c>
       <c r="F218" t="n">
-        <v>19911</v>
+        <v>17375</v>
       </c>
     </row>
     <row r="219">
@@ -11606,19 +11782,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>13792</v>
+        <v>19990</v>
       </c>
       <c r="C219" t="n">
-        <v>17498</v>
+        <v>22947</v>
       </c>
       <c r="D219" t="n">
         <v>12164</v>
       </c>
       <c r="E219" t="n">
-        <v>22947</v>
+        <v>13792</v>
       </c>
       <c r="F219" t="n">
-        <v>19990</v>
+        <v>17498</v>
       </c>
     </row>
     <row r="220">
@@ -11628,19 +11804,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>13872</v>
+        <v>20153</v>
       </c>
       <c r="C220" t="n">
-        <v>17481</v>
+        <v>22940</v>
       </c>
       <c r="D220" t="n">
         <v>12806</v>
       </c>
       <c r="E220" t="n">
-        <v>22940</v>
+        <v>13872</v>
       </c>
       <c r="F220" t="n">
-        <v>20153</v>
+        <v>17481</v>
       </c>
     </row>
     <row r="221">
@@ -11650,19 +11826,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>13621</v>
+        <v>20203</v>
       </c>
       <c r="C221" t="n">
-        <v>17477</v>
+        <v>23204</v>
       </c>
       <c r="D221" t="n">
         <v>12806</v>
       </c>
       <c r="E221" t="n">
-        <v>23204</v>
+        <v>13621</v>
       </c>
       <c r="F221" t="n">
-        <v>20203</v>
+        <v>17477</v>
       </c>
     </row>
     <row r="222">
@@ -11672,19 +11848,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>13621</v>
+        <v>20203</v>
       </c>
       <c r="C222" t="n">
-        <v>17477</v>
+        <v>23325</v>
       </c>
       <c r="D222" t="n">
         <v>13455</v>
       </c>
       <c r="E222" t="n">
-        <v>23325</v>
+        <v>13621</v>
       </c>
       <c r="F222" t="n">
-        <v>20203</v>
+        <v>17477</v>
       </c>
     </row>
     <row r="223">
@@ -11694,19 +11870,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>13792</v>
+        <v>20243</v>
       </c>
       <c r="C223" t="n">
-        <v>17274</v>
+        <v>23405</v>
       </c>
       <c r="D223" t="n">
         <v>13127</v>
       </c>
       <c r="E223" t="n">
-        <v>23405</v>
+        <v>13792</v>
       </c>
       <c r="F223" t="n">
-        <v>20243</v>
+        <v>17274</v>
       </c>
     </row>
     <row r="224">
@@ -11716,19 +11892,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>13717</v>
+        <v>20195</v>
       </c>
       <c r="C224" t="n">
-        <v>17188</v>
+        <v>23364</v>
       </c>
       <c r="D224" t="n">
         <v>13982</v>
       </c>
       <c r="E224" t="n">
-        <v>23364</v>
+        <v>13717</v>
       </c>
       <c r="F224" t="n">
-        <v>20195</v>
+        <v>17188</v>
       </c>
     </row>
     <row r="225">
@@ -11738,19 +11914,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>13717</v>
+        <v>20482</v>
       </c>
       <c r="C225" t="n">
-        <v>17143</v>
+        <v>23424</v>
       </c>
       <c r="D225" t="n">
         <v>13307</v>
       </c>
       <c r="E225" t="n">
-        <v>23424</v>
+        <v>13717</v>
       </c>
       <c r="F225" t="n">
-        <v>20482</v>
+        <v>17143</v>
       </c>
     </row>
     <row r="226">
@@ -11760,19 +11936,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>13717</v>
+        <v>20716</v>
       </c>
       <c r="C226" t="n">
-        <v>17357</v>
+        <v>23686</v>
       </c>
       <c r="D226" t="n">
         <v>13127</v>
       </c>
       <c r="E226" t="n">
-        <v>23686</v>
+        <v>13717</v>
       </c>
       <c r="F226" t="n">
-        <v>20716</v>
+        <v>17357</v>
       </c>
     </row>
     <row r="227">
@@ -11782,19 +11958,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>13479</v>
+        <v>21418</v>
       </c>
       <c r="C227" t="n">
-        <v>17163</v>
+        <v>24322</v>
       </c>
       <c r="D227" t="n">
         <v>13127</v>
       </c>
       <c r="E227" t="n">
-        <v>24322</v>
+        <v>13479</v>
       </c>
       <c r="F227" t="n">
-        <v>21418</v>
+        <v>17163</v>
       </c>
     </row>
     <row r="228">
@@ -11804,19 +11980,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>13313</v>
+        <v>21548</v>
       </c>
       <c r="C228" t="n">
-        <v>17080</v>
+        <v>24577</v>
       </c>
       <c r="D228" t="n">
         <v>13127</v>
       </c>
       <c r="E228" t="n">
-        <v>24577</v>
+        <v>13313</v>
       </c>
       <c r="F228" t="n">
-        <v>21548</v>
+        <v>17080</v>
       </c>
     </row>
     <row r="229">
@@ -11826,19 +12002,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>13133</v>
+        <v>21437</v>
       </c>
       <c r="C229" t="n">
-        <v>16922</v>
+        <v>24710</v>
       </c>
       <c r="D229" t="n">
         <v>12956</v>
       </c>
       <c r="E229" t="n">
-        <v>24710</v>
+        <v>13133</v>
       </c>
       <c r="F229" t="n">
-        <v>21437</v>
+        <v>16922</v>
       </c>
     </row>
     <row r="230">
@@ -11848,19 +12024,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>13133</v>
+        <v>21315</v>
       </c>
       <c r="C230" t="n">
-        <v>16922</v>
+        <v>24629</v>
       </c>
       <c r="D230" t="n">
         <v>12774</v>
       </c>
       <c r="E230" t="n">
-        <v>24629</v>
+        <v>13133</v>
       </c>
       <c r="F230" t="n">
-        <v>21315</v>
+        <v>16922</v>
       </c>
     </row>
     <row r="231">
@@ -11870,19 +12046,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>13213</v>
+        <v>21442</v>
       </c>
       <c r="C231" t="n">
-        <v>16971</v>
+        <v>24629</v>
       </c>
       <c r="D231" t="n">
         <v>12774</v>
       </c>
       <c r="E231" t="n">
-        <v>24629</v>
+        <v>13213</v>
       </c>
       <c r="F231" t="n">
-        <v>21442</v>
+        <v>16971</v>
       </c>
     </row>
     <row r="232">
@@ -11892,19 +12068,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>13213</v>
+        <v>21565</v>
       </c>
       <c r="C232" t="n">
-        <v>17021</v>
+        <v>24565</v>
       </c>
       <c r="D232" t="n">
         <v>12774</v>
       </c>
       <c r="E232" t="n">
-        <v>24565</v>
+        <v>13213</v>
       </c>
       <c r="F232" t="n">
-        <v>21565</v>
+        <v>17021</v>
       </c>
     </row>
     <row r="233">
@@ -11914,19 +12090,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>13213</v>
+        <v>21565</v>
       </c>
       <c r="C233" t="n">
-        <v>17021</v>
+        <v>24565</v>
       </c>
       <c r="D233" t="n">
         <v>12774</v>
       </c>
       <c r="E233" t="n">
-        <v>24565</v>
+        <v>13213</v>
       </c>
       <c r="F233" t="n">
-        <v>21565</v>
+        <v>17021</v>
       </c>
     </row>
     <row r="234">
@@ -11936,19 +12112,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>13133</v>
+        <v>21067</v>
       </c>
       <c r="C234" t="n">
-        <v>16949</v>
+        <v>24338</v>
       </c>
       <c r="D234" t="n">
         <v>12317</v>
       </c>
       <c r="E234" t="n">
-        <v>24338</v>
+        <v>13133</v>
       </c>
       <c r="F234" t="n">
-        <v>21067</v>
+        <v>16949</v>
       </c>
     </row>
     <row r="235">
@@ -11958,19 +12134,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>13133</v>
+        <v>20848</v>
       </c>
       <c r="C235" t="n">
-        <v>16809</v>
+        <v>24080</v>
       </c>
       <c r="D235" t="n">
         <v>12151</v>
       </c>
       <c r="E235" t="n">
-        <v>24080</v>
+        <v>13133</v>
       </c>
       <c r="F235" t="n">
-        <v>20848</v>
+        <v>16809</v>
       </c>
     </row>
     <row r="236">
@@ -11980,19 +12156,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>13133</v>
+        <v>20575</v>
       </c>
       <c r="C236" t="n">
-        <v>16781</v>
+        <v>24176</v>
       </c>
       <c r="D236" t="n">
         <v>12151</v>
       </c>
       <c r="E236" t="n">
-        <v>24176</v>
+        <v>13133</v>
       </c>
       <c r="F236" t="n">
-        <v>20575</v>
+        <v>16781</v>
       </c>
     </row>
     <row r="237">
@@ -12002,19 +12178,19 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>13133</v>
+        <v>20686</v>
       </c>
       <c r="C237" t="n">
-        <v>16781</v>
+        <v>24355</v>
       </c>
       <c r="D237" t="n">
         <v>12151</v>
       </c>
       <c r="E237" t="n">
-        <v>24355</v>
+        <v>13133</v>
       </c>
       <c r="F237" t="n">
-        <v>20686</v>
+        <v>16781</v>
       </c>
     </row>
     <row r="238">
@@ -12024,19 +12200,19 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>13313</v>
+        <v>20737</v>
       </c>
       <c r="C238" t="n">
-        <v>16691</v>
+        <v>24485</v>
       </c>
       <c r="D238" t="n">
         <v>12151</v>
       </c>
       <c r="E238" t="n">
-        <v>24485</v>
+        <v>13313</v>
       </c>
       <c r="F238" t="n">
-        <v>20737</v>
+        <v>16691</v>
       </c>
     </row>
     <row r="239">
@@ -12046,19 +12222,19 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>13313</v>
+        <v>20659</v>
       </c>
       <c r="C239" t="n">
-        <v>16733</v>
+        <v>24527</v>
       </c>
       <c r="D239" t="n">
         <v>12151</v>
       </c>
       <c r="E239" t="n">
-        <v>24527</v>
+        <v>13313</v>
       </c>
       <c r="F239" t="n">
-        <v>20659</v>
+        <v>16733</v>
       </c>
     </row>
     <row r="240">
@@ -12068,19 +12244,19 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>13394</v>
+        <v>20737</v>
       </c>
       <c r="C240" t="n">
-        <v>16768</v>
+        <v>24485</v>
       </c>
       <c r="D240" t="n">
         <v>12151</v>
       </c>
       <c r="E240" t="n">
-        <v>24485</v>
+        <v>13394</v>
       </c>
       <c r="F240" t="n">
-        <v>20737</v>
+        <v>16768</v>
       </c>
     </row>
     <row r="241">
@@ -12090,19 +12266,19 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>14226</v>
+        <v>20803</v>
       </c>
       <c r="C241" t="n">
-        <v>16664</v>
+        <v>24268</v>
       </c>
       <c r="D241" t="n">
         <v>12637</v>
       </c>
       <c r="E241" t="n">
-        <v>24268</v>
+        <v>14226</v>
       </c>
       <c r="F241" t="n">
-        <v>20803</v>
+        <v>16664</v>
       </c>
     </row>
     <row r="242">
@@ -12112,19 +12288,19 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>14226</v>
+        <v>20841</v>
       </c>
       <c r="C242" t="n">
-        <v>16622</v>
+        <v>24058</v>
       </c>
       <c r="D242" t="n">
         <v>12637</v>
       </c>
       <c r="E242" t="n">
-        <v>24058</v>
+        <v>14226</v>
       </c>
       <c r="F242" t="n">
-        <v>20841</v>
+        <v>16622</v>
       </c>
     </row>
     <row r="243">
@@ -12134,19 +12310,19 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>13979</v>
+        <v>20734</v>
       </c>
       <c r="C243" t="n">
-        <v>16584</v>
+        <v>24188</v>
       </c>
       <c r="D243" t="n">
         <v>12305</v>
       </c>
       <c r="E243" t="n">
-        <v>24188</v>
+        <v>13979</v>
       </c>
       <c r="F243" t="n">
-        <v>20734</v>
+        <v>16584</v>
       </c>
     </row>
     <row r="244">
@@ -12156,19 +12332,19 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>14200</v>
+        <v>20764</v>
       </c>
       <c r="C244" t="n">
-        <v>16716</v>
+        <v>24266</v>
       </c>
       <c r="D244" t="n">
         <v>12305</v>
       </c>
       <c r="E244" t="n">
-        <v>24266</v>
+        <v>14200</v>
       </c>
       <c r="F244" t="n">
-        <v>20764</v>
+        <v>16716</v>
       </c>
     </row>
     <row r="245">
@@ -12178,19 +12354,19 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>14175</v>
+        <v>20916</v>
       </c>
       <c r="C245" t="n">
-        <v>16716</v>
+        <v>24353</v>
       </c>
       <c r="D245" t="n">
         <v>12305</v>
       </c>
       <c r="E245" t="n">
-        <v>24353</v>
+        <v>14175</v>
       </c>
       <c r="F245" t="n">
-        <v>20916</v>
+        <v>16716</v>
       </c>
     </row>
     <row r="246">
@@ -12200,19 +12376,19 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>14092</v>
+        <v>20826</v>
       </c>
       <c r="C246" t="n">
-        <v>16684</v>
+        <v>24222</v>
       </c>
       <c r="D246" t="n">
         <v>12305</v>
       </c>
       <c r="E246" t="n">
-        <v>24222</v>
+        <v>14092</v>
       </c>
       <c r="F246" t="n">
-        <v>20826</v>
+        <v>16684</v>
       </c>
     </row>
     <row r="247">
@@ -12222,19 +12398,19 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>14092</v>
+        <v>20746</v>
       </c>
       <c r="C247" t="n">
-        <v>16641</v>
+        <v>24171</v>
       </c>
       <c r="D247" t="n">
         <v>12792</v>
       </c>
       <c r="E247" t="n">
-        <v>24171</v>
+        <v>14092</v>
       </c>
       <c r="F247" t="n">
-        <v>20746</v>
+        <v>16641</v>
       </c>
     </row>
     <row r="248">
@@ -12244,19 +12420,19 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>14425</v>
+        <v>20875</v>
       </c>
       <c r="C248" t="n">
-        <v>16671</v>
+        <v>24119</v>
       </c>
       <c r="D248" t="n">
         <v>13325</v>
       </c>
       <c r="E248" t="n">
-        <v>24119</v>
+        <v>14425</v>
       </c>
       <c r="F248" t="n">
-        <v>20875</v>
+        <v>16671</v>
       </c>
     </row>
     <row r="249">
@@ -12266,19 +12442,19 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>14290</v>
+        <v>20509</v>
       </c>
       <c r="C249" t="n">
-        <v>16457</v>
+        <v>23755</v>
       </c>
       <c r="D249" t="n">
         <v>13325</v>
       </c>
       <c r="E249" t="n">
-        <v>23755</v>
+        <v>14290</v>
       </c>
       <c r="F249" t="n">
-        <v>20509</v>
+        <v>16457</v>
       </c>
     </row>
     <row r="250">
@@ -12288,19 +12464,19 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>14059</v>
+        <v>20628</v>
       </c>
       <c r="C250" t="n">
-        <v>16444</v>
+        <v>23776</v>
       </c>
       <c r="D250" t="n">
         <v>13325</v>
       </c>
       <c r="E250" t="n">
-        <v>23776</v>
+        <v>14059</v>
       </c>
       <c r="F250" t="n">
-        <v>20628</v>
+        <v>16444</v>
       </c>
     </row>
     <row r="251">
@@ -12310,19 +12486,19 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>14135</v>
+        <v>20714</v>
       </c>
       <c r="C251" t="n">
-        <v>16538</v>
+        <v>23818</v>
       </c>
       <c r="D251" t="n">
         <v>13658</v>
       </c>
       <c r="E251" t="n">
-        <v>23818</v>
+        <v>14135</v>
       </c>
       <c r="F251" t="n">
-        <v>20714</v>
+        <v>16538</v>
       </c>
     </row>
     <row r="252">
@@ -12332,19 +12508,19 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>14176</v>
+        <v>20965</v>
       </c>
       <c r="C252" t="n">
-        <v>16826</v>
+        <v>24223</v>
       </c>
       <c r="D252" t="n">
         <v>13658</v>
       </c>
       <c r="E252" t="n">
-        <v>24223</v>
+        <v>14176</v>
       </c>
       <c r="F252" t="n">
-        <v>20965</v>
+        <v>16826</v>
       </c>
     </row>
     <row r="253">
@@ -12354,19 +12530,19 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>14339</v>
+        <v>21259</v>
       </c>
       <c r="C253" t="n">
-        <v>16957</v>
+        <v>24937</v>
       </c>
       <c r="D253" t="n">
         <v>13658</v>
       </c>
       <c r="E253" t="n">
-        <v>24937</v>
+        <v>14339</v>
       </c>
       <c r="F253" t="n">
-        <v>21259</v>
+        <v>16957</v>
       </c>
     </row>
     <row r="254">
@@ -12376,19 +12552,19 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>14339</v>
+        <v>21628</v>
       </c>
       <c r="C254" t="n">
-        <v>16979</v>
+        <v>25406</v>
       </c>
       <c r="D254" t="n">
         <v>13658</v>
       </c>
       <c r="E254" t="n">
-        <v>25406</v>
+        <v>14339</v>
       </c>
       <c r="F254" t="n">
-        <v>21628</v>
+        <v>16979</v>
       </c>
     </row>
     <row r="255">
@@ -12398,19 +12574,19 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>14649</v>
+        <v>22180</v>
       </c>
       <c r="C255" t="n">
-        <v>17252</v>
+        <v>25791</v>
       </c>
       <c r="D255" t="n">
         <v>13658</v>
       </c>
       <c r="E255" t="n">
-        <v>25791</v>
+        <v>14649</v>
       </c>
       <c r="F255" t="n">
-        <v>22180</v>
+        <v>17252</v>
       </c>
     </row>
     <row r="256">
@@ -12420,19 +12596,19 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>14784</v>
+        <v>22685</v>
       </c>
       <c r="C256" t="n">
-        <v>17343</v>
+        <v>26206</v>
       </c>
       <c r="D256" t="n">
         <v>14000</v>
       </c>
       <c r="E256" t="n">
-        <v>26206</v>
+        <v>14784</v>
       </c>
       <c r="F256" t="n">
-        <v>22685</v>
+        <v>17343</v>
       </c>
     </row>
     <row r="257">
@@ -12442,19 +12618,19 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>14936</v>
+        <v>23472</v>
       </c>
       <c r="C257" t="n">
-        <v>18073</v>
+        <v>27198</v>
       </c>
       <c r="D257" t="n">
         <v>14326</v>
       </c>
       <c r="E257" t="n">
-        <v>27198</v>
+        <v>14936</v>
       </c>
       <c r="F257" t="n">
-        <v>23472</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="258">
@@ -12464,19 +12640,19 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>15529</v>
+        <v>23976</v>
       </c>
       <c r="C258" t="n">
-        <v>18484</v>
+        <v>27935</v>
       </c>
       <c r="D258" t="n">
         <v>14326</v>
       </c>
       <c r="E258" t="n">
-        <v>27935</v>
+        <v>15529</v>
       </c>
       <c r="F258" t="n">
-        <v>23976</v>
+        <v>18484</v>
       </c>
     </row>
     <row r="259">
@@ -12486,19 +12662,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>15604</v>
+        <v>24172</v>
       </c>
       <c r="C259" t="n">
-        <v>18849</v>
+        <v>28287</v>
       </c>
       <c r="D259" t="n">
         <v>14820</v>
       </c>
       <c r="E259" t="n">
-        <v>28287</v>
+        <v>15604</v>
       </c>
       <c r="F259" t="n">
-        <v>24172</v>
+        <v>18849</v>
       </c>
     </row>
     <row r="260">
@@ -12508,19 +12684,19 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>15734</v>
+        <v>24254</v>
       </c>
       <c r="C260" t="n">
-        <v>18919</v>
+        <v>28525</v>
       </c>
       <c r="D260" t="n">
         <v>14820</v>
       </c>
       <c r="E260" t="n">
-        <v>28525</v>
+        <v>15734</v>
       </c>
       <c r="F260" t="n">
-        <v>24254</v>
+        <v>18919</v>
       </c>
     </row>
     <row r="261">
@@ -12530,19 +12706,19 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>15875</v>
+        <v>24726</v>
       </c>
       <c r="C261" t="n">
-        <v>19314</v>
+        <v>28926</v>
       </c>
       <c r="D261" t="n">
         <v>14820</v>
       </c>
       <c r="E261" t="n">
-        <v>28926</v>
+        <v>15875</v>
       </c>
       <c r="F261" t="n">
-        <v>24726</v>
+        <v>19314</v>
       </c>
     </row>
     <row r="262">
@@ -12552,19 +12728,19 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>15875</v>
+        <v>24765</v>
       </c>
       <c r="C262" t="n">
-        <v>19314</v>
+        <v>28986</v>
       </c>
       <c r="D262" t="n">
         <v>14820</v>
       </c>
       <c r="E262" t="n">
-        <v>28986</v>
+        <v>15875</v>
       </c>
       <c r="F262" t="n">
-        <v>24765</v>
+        <v>19314</v>
       </c>
     </row>
     <row r="263">
@@ -12574,19 +12750,19 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>16022</v>
+        <v>25306</v>
       </c>
       <c r="C263" t="n">
-        <v>20303</v>
+        <v>29352</v>
       </c>
       <c r="D263" t="n">
         <v>14820</v>
       </c>
       <c r="E263" t="n">
-        <v>29352</v>
+        <v>16022</v>
       </c>
       <c r="F263" t="n">
-        <v>25306</v>
+        <v>20303</v>
       </c>
     </row>
     <row r="264">
@@ -12596,19 +12772,19 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>16022</v>
+        <v>25841</v>
       </c>
       <c r="C264" t="n">
-        <v>21197</v>
+        <v>29612</v>
       </c>
       <c r="D264" t="n">
         <v>15132</v>
       </c>
       <c r="E264" t="n">
-        <v>29612</v>
+        <v>16022</v>
       </c>
       <c r="F264" t="n">
-        <v>25841</v>
+        <v>21197</v>
       </c>
     </row>
     <row r="265">
@@ -12618,19 +12794,19 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>16092</v>
+        <v>26285</v>
       </c>
       <c r="C265" t="n">
-        <v>21185</v>
+        <v>30179</v>
       </c>
       <c r="D265" t="n">
         <v>15767</v>
       </c>
       <c r="E265" t="n">
-        <v>30179</v>
+        <v>16092</v>
       </c>
       <c r="F265" t="n">
-        <v>26285</v>
+        <v>21185</v>
       </c>
     </row>
     <row r="266">
@@ -12640,19 +12816,19 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>16774</v>
+        <v>26515</v>
       </c>
       <c r="C266" t="n">
-        <v>21435</v>
+        <v>30417</v>
       </c>
       <c r="D266" t="n">
         <v>15767</v>
       </c>
       <c r="E266" t="n">
-        <v>30417</v>
+        <v>16774</v>
       </c>
       <c r="F266" t="n">
-        <v>26515</v>
+        <v>21435</v>
       </c>
     </row>
     <row r="267">
@@ -12662,19 +12838,19 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>16705</v>
+        <v>26976</v>
       </c>
       <c r="C267" t="n">
-        <v>21984</v>
+        <v>30887</v>
       </c>
       <c r="D267" t="n">
         <v>15461</v>
       </c>
       <c r="E267" t="n">
-        <v>30887</v>
+        <v>16705</v>
       </c>
       <c r="F267" t="n">
-        <v>26976</v>
+        <v>21984</v>
       </c>
     </row>
     <row r="268">
@@ -12684,19 +12860,19 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>17433</v>
+        <v>28328</v>
       </c>
       <c r="C268" t="n">
-        <v>23724</v>
+        <v>31819</v>
       </c>
       <c r="D268" t="n">
         <v>15461</v>
       </c>
       <c r="E268" t="n">
-        <v>31819</v>
+        <v>17433</v>
       </c>
       <c r="F268" t="n">
-        <v>28328</v>
+        <v>23724</v>
       </c>
     </row>
     <row r="269">
@@ -12706,19 +12882,19 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>17575</v>
+        <v>28545</v>
       </c>
       <c r="C269" t="n">
-        <v>24984</v>
+        <v>32733</v>
       </c>
       <c r="D269" t="n">
         <v>15616</v>
       </c>
       <c r="E269" t="n">
-        <v>32733</v>
+        <v>17575</v>
       </c>
       <c r="F269" t="n">
-        <v>28545</v>
+        <v>24984</v>
       </c>
     </row>
     <row r="270">
@@ -12728,19 +12904,19 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>18340</v>
+        <v>28913</v>
       </c>
       <c r="C270" t="n">
-        <v>25483</v>
+        <v>33802</v>
       </c>
       <c r="D270" t="n">
         <v>15616</v>
       </c>
       <c r="E270" t="n">
-        <v>33802</v>
+        <v>18340</v>
       </c>
       <c r="F270" t="n">
-        <v>28913</v>
+        <v>25483</v>
       </c>
     </row>
     <row r="271">
@@ -12750,19 +12926,19 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>17954</v>
+        <v>29880</v>
       </c>
       <c r="C271" t="n">
-        <v>25729</v>
+        <v>34707</v>
       </c>
       <c r="D271" t="n">
         <v>19310</v>
       </c>
       <c r="E271" t="n">
-        <v>34707</v>
+        <v>17954</v>
       </c>
       <c r="F271" t="n">
-        <v>29880</v>
+        <v>25729</v>
       </c>
     </row>
     <row r="272">
@@ -12772,19 +12948,19 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>17812</v>
+        <v>30521</v>
       </c>
       <c r="C272" t="n">
-        <v>26337</v>
+        <v>35436</v>
       </c>
       <c r="D272" t="n">
         <v>19626</v>
       </c>
       <c r="E272" t="n">
-        <v>35436</v>
+        <v>17812</v>
       </c>
       <c r="F272" t="n">
-        <v>30521</v>
+        <v>26337</v>
       </c>
     </row>
     <row r="273">
@@ -12794,19 +12970,19 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>18245</v>
+        <v>30820</v>
       </c>
       <c r="C273" t="n">
-        <v>26506</v>
+        <v>35848</v>
       </c>
       <c r="D273" t="n">
         <v>19626</v>
       </c>
       <c r="E273" t="n">
-        <v>35848</v>
+        <v>18245</v>
       </c>
       <c r="F273" t="n">
-        <v>30820</v>
+        <v>26506</v>
       </c>
     </row>
     <row r="274">
@@ -12816,19 +12992,19 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>18108</v>
+        <v>31474</v>
       </c>
       <c r="C274" t="n">
-        <v>26740</v>
+        <v>36669</v>
       </c>
       <c r="D274" t="n">
         <v>20260</v>
       </c>
       <c r="E274" t="n">
-        <v>36669</v>
+        <v>18108</v>
       </c>
       <c r="F274" t="n">
-        <v>31474</v>
+        <v>26740</v>
       </c>
     </row>
     <row r="275">
@@ -12838,19 +13014,19 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>18108</v>
+        <v>32329</v>
       </c>
       <c r="C275" t="n">
-        <v>26651</v>
+        <v>37101</v>
       </c>
       <c r="D275" t="n">
         <v>21328</v>
       </c>
       <c r="E275" t="n">
-        <v>37101</v>
+        <v>18108</v>
       </c>
       <c r="F275" t="n">
-        <v>32329</v>
+        <v>26651</v>
       </c>
     </row>
     <row r="276">
@@ -12860,19 +13036,19 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>18525</v>
+        <v>33742</v>
       </c>
       <c r="C276" t="n">
-        <v>27666</v>
+        <v>37835</v>
       </c>
       <c r="D276" t="n">
         <v>21661</v>
       </c>
       <c r="E276" t="n">
-        <v>37835</v>
+        <v>18525</v>
       </c>
       <c r="F276" t="n">
-        <v>33742</v>
+        <v>27666</v>
       </c>
     </row>
     <row r="277">
@@ -12882,19 +13058,19 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>18713</v>
+        <v>33883</v>
       </c>
       <c r="C277" t="n">
-        <v>27763</v>
+        <v>38210</v>
       </c>
       <c r="D277" t="n">
         <v>20824</v>
       </c>
       <c r="E277" t="n">
-        <v>38210</v>
+        <v>18713</v>
       </c>
       <c r="F277" t="n">
-        <v>33883</v>
+        <v>27763</v>
       </c>
     </row>
     <row r="278">
@@ -12904,19 +13080,19 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>18713</v>
+        <v>33883</v>
       </c>
       <c r="C278" t="n">
-        <v>27413</v>
+        <v>38125</v>
       </c>
       <c r="D278" t="n">
         <v>20488</v>
       </c>
       <c r="E278" t="n">
-        <v>38125</v>
+        <v>18713</v>
       </c>
       <c r="F278" t="n">
-        <v>33883</v>
+        <v>27413</v>
       </c>
     </row>
     <row r="279">
@@ -12926,19 +13102,19 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>18713</v>
+        <v>34222</v>
       </c>
       <c r="C279" t="n">
-        <v>27850</v>
+        <v>38619</v>
       </c>
       <c r="D279" t="n">
         <v>21312</v>
       </c>
       <c r="E279" t="n">
-        <v>38619</v>
+        <v>18713</v>
       </c>
       <c r="F279" t="n">
-        <v>34222</v>
+        <v>27850</v>
       </c>
     </row>
     <row r="280">
@@ -12948,19 +13124,19 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>18327</v>
+        <v>33882</v>
       </c>
       <c r="C280" t="n">
-        <v>27706</v>
+        <v>38585</v>
       </c>
       <c r="D280" t="n">
         <v>21312</v>
       </c>
       <c r="E280" t="n">
-        <v>38585</v>
+        <v>18327</v>
       </c>
       <c r="F280" t="n">
-        <v>33882</v>
+        <v>27706</v>
       </c>
     </row>
     <row r="281">
@@ -12970,19 +13146,19 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>18525</v>
+        <v>33772</v>
       </c>
       <c r="C281" t="n">
-        <v>27668</v>
+        <v>38500</v>
       </c>
       <c r="D281" t="n">
         <v>22420</v>
       </c>
       <c r="E281" t="n">
-        <v>38500</v>
+        <v>18525</v>
       </c>
       <c r="F281" t="n">
-        <v>33772</v>
+        <v>27668</v>
       </c>
     </row>
     <row r="282">
@@ -12992,19 +13168,19 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>18713</v>
+        <v>33685</v>
       </c>
       <c r="C282" t="n">
-        <v>27798</v>
+        <v>38504</v>
       </c>
       <c r="D282" t="n">
         <v>22420</v>
       </c>
       <c r="E282" t="n">
-        <v>38504</v>
+        <v>18713</v>
       </c>
       <c r="F282" t="n">
-        <v>33685</v>
+        <v>27798</v>
       </c>
     </row>
     <row r="283">
@@ -13014,19 +13190,19 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>18327</v>
+        <v>32470</v>
       </c>
       <c r="C283" t="n">
-        <v>27417</v>
+        <v>37878</v>
       </c>
       <c r="D283" t="n">
         <v>20646</v>
       </c>
       <c r="E283" t="n">
-        <v>37878</v>
+        <v>18327</v>
       </c>
       <c r="F283" t="n">
-        <v>32470</v>
+        <v>27417</v>
       </c>
     </row>
     <row r="284">
@@ -13036,19 +13212,19 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>18525</v>
+        <v>32520</v>
       </c>
       <c r="C284" t="n">
-        <v>27342</v>
+        <v>37767</v>
       </c>
       <c r="D284" t="n">
         <v>21898</v>
       </c>
       <c r="E284" t="n">
-        <v>37767</v>
+        <v>18525</v>
       </c>
       <c r="F284" t="n">
-        <v>32520</v>
+        <v>27342</v>
       </c>
     </row>
     <row r="285">
@@ -13058,19 +13234,19 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>18243</v>
+        <v>32230</v>
       </c>
       <c r="C285" t="n">
-        <v>27063</v>
+        <v>37223</v>
       </c>
       <c r="D285" t="n">
         <v>20646</v>
       </c>
       <c r="E285" t="n">
-        <v>37223</v>
+        <v>18243</v>
       </c>
       <c r="F285" t="n">
-        <v>32230</v>
+        <v>27063</v>
       </c>
     </row>
     <row r="286">
@@ -13080,19 +13256,19 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>18440</v>
+        <v>31680</v>
       </c>
       <c r="C286" t="n">
-        <v>26152</v>
+        <v>36611</v>
       </c>
       <c r="D286" t="n">
         <v>20328</v>
       </c>
       <c r="E286" t="n">
-        <v>36611</v>
+        <v>18440</v>
       </c>
       <c r="F286" t="n">
-        <v>31680</v>
+        <v>26152</v>
       </c>
     </row>
     <row r="287">
@@ -13102,19 +13278,19 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>18354</v>
+        <v>31530</v>
       </c>
       <c r="C287" t="n">
-        <v>25882</v>
+        <v>35508</v>
       </c>
       <c r="D287" t="n">
         <v>20824</v>
       </c>
       <c r="E287" t="n">
-        <v>35508</v>
+        <v>18354</v>
       </c>
       <c r="F287" t="n">
-        <v>31530</v>
+        <v>25882</v>
       </c>
     </row>
     <row r="288">
@@ -13124,19 +13300,195 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>18436</v>
+        <v>31269</v>
       </c>
       <c r="C288" t="n">
-        <v>25930</v>
+        <v>35552</v>
       </c>
       <c r="D288" t="n">
         <v>20824</v>
       </c>
       <c r="E288" t="n">
-        <v>35552</v>
+        <v>18436</v>
       </c>
       <c r="F288" t="n">
-        <v>31269</v>
+        <v>25930</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>31457</v>
+      </c>
+      <c r="C289" t="n">
+        <v>35724</v>
+      </c>
+      <c r="D289" t="n">
+        <v>20984</v>
+      </c>
+      <c r="E289" t="n">
+        <v>18464</v>
+      </c>
+      <c r="F289" t="n">
+        <v>26342</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>31186</v>
+      </c>
+      <c r="C290" t="n">
+        <v>34821</v>
+      </c>
+      <c r="D290" t="n">
+        <v>20984</v>
+      </c>
+      <c r="E290" t="n">
+        <v>18539</v>
+      </c>
+      <c r="F290" t="n">
+        <v>26294</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>31091</v>
+      </c>
+      <c r="C291" t="n">
+        <v>34821</v>
+      </c>
+      <c r="D291" t="n">
+        <v>20824</v>
+      </c>
+      <c r="E291" t="n">
+        <v>18449</v>
+      </c>
+      <c r="F291" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>31106</v>
+      </c>
+      <c r="C292" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D292" t="n">
+        <v>20824</v>
+      </c>
+      <c r="E292" t="n">
+        <v>18116</v>
+      </c>
+      <c r="F292" t="n">
+        <v>25923</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>30804</v>
+      </c>
+      <c r="C293" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D293" t="n">
+        <v>20661</v>
+      </c>
+      <c r="E293" t="n">
+        <v>18389</v>
+      </c>
+      <c r="F293" t="n">
+        <v>25674</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>30695</v>
+      </c>
+      <c r="C294" t="n">
+        <v>34737</v>
+      </c>
+      <c r="D294" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E294" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F294" t="n">
+        <v>25519</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>30270</v>
+      </c>
+      <c r="C295" t="n">
+        <v>34376</v>
+      </c>
+      <c r="D295" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E295" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F295" t="n">
+        <v>25480</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>29709</v>
+      </c>
+      <c r="C296" t="n">
+        <v>33663</v>
+      </c>
+      <c r="D296" t="n">
+        <v>20328</v>
+      </c>
+      <c r="E296" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F296" t="n">
+        <v>25434</v>
       </c>
     </row>
   </sheetData>
